--- a/src/assets/abapi_data/api_data_all.xlsx
+++ b/src/assets/abapi_data/api_data_all.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\abapi_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ps_LDMS\src\assets\abapi_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{19CFCEEA-A1A4-41CA-94A3-F42E29C495BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5ED6C98-83CC-401C-982E-5BE5A8369B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="240" windowWidth="29040" windowHeight="16080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Payload" sheetId="8" r:id="rId1"/>
@@ -2085,27 +2085,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2163,6 +2142,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2170,6 +2170,74 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2186,7 +2254,7 @@
   <a:themeElements>
     <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr val="windowText" lastClr="171717"/>
       </a:dk1>
       <a:lt1>
         <a:sysClr val="window" lastClr="FFFFFF"/>
@@ -2613,7 +2681,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="25">
         <v>8</v>
       </c>
@@ -2664,7 +2732,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="25">
         <v>11</v>
       </c>
@@ -2681,7 +2749,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="25">
         <v>12</v>
       </c>
@@ -2698,7 +2766,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="25">
         <v>13</v>
       </c>
@@ -2732,7 +2800,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="25">
         <v>15</v>
       </c>
@@ -2749,7 +2817,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="25">
         <v>16</v>
       </c>
@@ -2800,14 +2868,19 @@
         <v>542</v>
       </c>
     </row>
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="54" t="s">
         <v>548</v>
       </c>
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
+      <c r="B25" s="55"/>
+      <c r="C25" s="55"/>
+      <c r="D25" s="55"/>
+      <c r="E25" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2834,830 +2907,830 @@
   <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" style="40" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" style="40" customWidth="1"/>
-    <col min="3" max="3" width="24.85546875" style="40" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="32.140625" style="40" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="30.7109375" style="40" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" style="40" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="40"/>
+    <col min="1" max="1" width="16.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="33" customWidth="1"/>
+    <col min="3" max="3" width="24.85546875" style="33" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="32.140625" style="33" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="30.7109375" style="33" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" style="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="33"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="30" t="s">
         <v>551</v>
       </c>
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="30" t="s">
         <v>550</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="31" t="s">
         <v>485</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" s="30" t="s">
         <v>486</v>
       </c>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="31" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="39">
+      <c r="A2" s="32">
         <v>119</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="39" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="39">
+      <c r="C2" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="32">
         <f>A2</f>
         <v>119</v>
       </c>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39">
+      <c r="E2" s="32"/>
+      <c r="F2" s="32">
         <v>31312</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="39">
+      <c r="A3" s="32">
         <v>121</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="39" t="s">
+      <c r="C3" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="39">
+      <c r="D3" s="32">
         <f t="shared" ref="D3:D43" si="0">A3</f>
         <v>121</v>
       </c>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39">
+      <c r="E3" s="32"/>
+      <c r="F3" s="32">
         <v>31313</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="39">
+      <c r="A4" s="32">
         <v>640</v>
       </c>
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="39">
+      <c r="D4" s="32">
         <f t="shared" si="0"/>
         <v>640</v>
       </c>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39">
+      <c r="E4" s="32"/>
+      <c r="F4" s="32">
         <v>31314</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="39">
+      <c r="A5" s="32">
         <v>126</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="C5" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="39">
+      <c r="D5" s="32">
         <f t="shared" si="0"/>
         <v>126</v>
       </c>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39">
+      <c r="E5" s="32"/>
+      <c r="F5" s="32">
         <v>31321</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="39">
+      <c r="A6" s="32">
         <v>128</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="39" t="s">
+      <c r="C6" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="39">
+      <c r="D6" s="32">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39">
+      <c r="E6" s="32"/>
+      <c r="F6" s="32">
         <v>31322</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="39">
+      <c r="A7" s="32">
         <v>129</v>
       </c>
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="39" t="s">
+      <c r="C7" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="32">
         <f t="shared" si="0"/>
         <v>129</v>
       </c>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39">
+      <c r="E7" s="32"/>
+      <c r="F7" s="32">
         <v>31323</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="39">
+      <c r="A8" s="32">
         <v>130</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="39" t="s">
+      <c r="C8" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="39">
+      <c r="D8" s="32">
         <f t="shared" si="0"/>
         <v>130</v>
       </c>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39">
+      <c r="E8" s="32"/>
+      <c r="F8" s="32">
         <v>31324</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="39">
+      <c r="A9" s="32">
         <v>131</v>
       </c>
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="32">
         <f t="shared" si="0"/>
         <v>131</v>
       </c>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39">
+      <c r="E9" s="32"/>
+      <c r="F9" s="32">
         <v>31325</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="39">
+      <c r="A10" s="32">
         <v>132</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="39">
+      <c r="D10" s="32">
         <f t="shared" si="0"/>
         <v>132</v>
       </c>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39">
+      <c r="E10" s="32"/>
+      <c r="F10" s="32">
         <v>31017</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="39">
+      <c r="A11" s="32">
         <v>133</v>
       </c>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="39">
+      <c r="D11" s="32">
         <f t="shared" si="0"/>
         <v>133</v>
       </c>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39">
+      <c r="E11" s="32"/>
+      <c r="F11" s="32">
         <v>31018</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="39">
+      <c r="A12" s="32">
         <v>137</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="39">
+      <c r="D12" s="32">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39">
+      <c r="E12" s="32"/>
+      <c r="F12" s="32">
         <v>31329</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="39">
+      <c r="A13" s="32">
         <v>138</v>
       </c>
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="39">
+      <c r="D13" s="32">
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39">
+      <c r="E13" s="32"/>
+      <c r="F13" s="32">
         <v>31330</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="39">
+      <c r="A14" s="32">
         <v>141</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="39">
+      <c r="D14" s="32">
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39">
+      <c r="E14" s="32"/>
+      <c r="F14" s="32">
         <v>31332</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="39">
+      <c r="A15" s="32">
         <v>146</v>
       </c>
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C15" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="39">
+      <c r="D15" s="32">
         <f t="shared" si="0"/>
         <v>146</v>
       </c>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39">
+      <c r="E15" s="32"/>
+      <c r="F15" s="32">
         <v>31337</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="39">
+      <c r="A16" s="32">
         <v>147</v>
       </c>
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="39" t="s">
+      <c r="C16" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="39">
+      <c r="D16" s="32">
         <f t="shared" si="0"/>
         <v>147</v>
       </c>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39">
+      <c r="E16" s="32"/>
+      <c r="F16" s="32">
         <v>31338</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="39">
+      <c r="A17" s="32">
         <v>148</v>
       </c>
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="39">
+      <c r="D17" s="32">
         <f t="shared" si="0"/>
         <v>148</v>
       </c>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39">
+      <c r="E17" s="32"/>
+      <c r="F17" s="32">
         <v>31339</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="39">
+      <c r="A18" s="32">
         <v>150</v>
       </c>
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="39" t="s">
+      <c r="C18" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="39">
+      <c r="D18" s="32">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39">
+      <c r="E18" s="32"/>
+      <c r="F18" s="32">
         <v>31342</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="39">
+      <c r="A19" s="32">
         <v>151</v>
       </c>
-      <c r="B19" s="39" t="s">
+      <c r="B19" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="39" t="s">
+      <c r="C19" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="39">
+      <c r="D19" s="32">
         <f t="shared" si="0"/>
         <v>151</v>
       </c>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39">
+      <c r="E19" s="32"/>
+      <c r="F19" s="32">
         <v>31344</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="39">
+      <c r="A20" s="32">
         <v>152</v>
       </c>
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="39" t="s">
+      <c r="C20" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="39">
+      <c r="D20" s="32">
         <f t="shared" si="0"/>
         <v>152</v>
       </c>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39">
+      <c r="E20" s="32"/>
+      <c r="F20" s="32">
         <v>31345</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="39">
+      <c r="A21" s="32">
         <v>633</v>
       </c>
-      <c r="B21" s="39" t="s">
+      <c r="B21" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="39" t="s">
+      <c r="C21" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="D21" s="39">
+      <c r="D21" s="32">
         <f t="shared" si="0"/>
         <v>633</v>
       </c>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39">
+      <c r="E21" s="32"/>
+      <c r="F21" s="32">
         <v>31349</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="39">
+      <c r="A22" s="32">
         <v>158</v>
       </c>
-      <c r="B22" s="39" t="s">
+      <c r="B22" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="39" t="s">
+      <c r="C22" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="D22" s="39">
+      <c r="D22" s="32">
         <f t="shared" si="0"/>
         <v>158</v>
       </c>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39">
+      <c r="E22" s="32"/>
+      <c r="F22" s="32">
         <v>31350</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="39">
+      <c r="A23" s="32">
         <v>159</v>
       </c>
-      <c r="B23" s="39" t="s">
+      <c r="B23" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="39" t="s">
+      <c r="C23" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="D23" s="39">
+      <c r="D23" s="32">
         <f t="shared" si="0"/>
         <v>159</v>
       </c>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39">
+      <c r="E23" s="32"/>
+      <c r="F23" s="32">
         <v>31351</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="39">
+      <c r="A24" s="32">
         <v>160</v>
       </c>
-      <c r="B24" s="39" t="s">
+      <c r="B24" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="39" t="s">
+      <c r="C24" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="D24" s="39">
+      <c r="D24" s="32">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39">
+      <c r="E24" s="32"/>
+      <c r="F24" s="32">
         <v>31352</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="39">
+      <c r="A25" s="32">
         <v>161</v>
       </c>
-      <c r="B25" s="39" t="s">
+      <c r="B25" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="39" t="s">
+      <c r="C25" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D25" s="39">
+      <c r="D25" s="32">
         <f t="shared" si="0"/>
         <v>161</v>
       </c>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39">
+      <c r="E25" s="32"/>
+      <c r="F25" s="32">
         <v>31353</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="39">
+      <c r="A26" s="32">
         <v>165</v>
       </c>
-      <c r="B26" s="39" t="s">
+      <c r="B26" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="39" t="s">
+      <c r="C26" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="D26" s="39">
+      <c r="D26" s="32">
         <f t="shared" si="0"/>
         <v>165</v>
       </c>
-      <c r="E26" s="39"/>
-      <c r="F26" s="39">
+      <c r="E26" s="32"/>
+      <c r="F26" s="32">
         <v>31356</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="39">
+      <c r="A27" s="32">
         <v>164</v>
       </c>
-      <c r="B27" s="39" t="s">
+      <c r="B27" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="39" t="s">
+      <c r="C27" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="D27" s="39">
+      <c r="D27" s="32">
         <f t="shared" si="0"/>
         <v>164</v>
       </c>
-      <c r="E27" s="39"/>
-      <c r="F27" s="39">
+      <c r="E27" s="32"/>
+      <c r="F27" s="32">
         <v>31355</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="39">
+      <c r="A28" s="32">
         <v>170</v>
       </c>
-      <c r="B28" s="39" t="s">
+      <c r="B28" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="39" t="s">
+      <c r="C28" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="D28" s="39">
+      <c r="D28" s="32">
         <f t="shared" si="0"/>
         <v>170</v>
       </c>
-      <c r="E28" s="39"/>
-      <c r="F28" s="39">
+      <c r="E28" s="32"/>
+      <c r="F28" s="32">
         <v>31361</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="39">
+      <c r="A29" s="32">
         <v>173</v>
       </c>
-      <c r="B29" s="39" t="s">
+      <c r="B29" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="39" t="s">
+      <c r="C29" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="D29" s="39">
+      <c r="D29" s="32">
         <f t="shared" si="0"/>
         <v>173</v>
       </c>
-      <c r="E29" s="39"/>
-      <c r="F29" s="39">
+      <c r="E29" s="32"/>
+      <c r="F29" s="32">
         <v>31364</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="39">
+      <c r="A30" s="32">
         <v>120</v>
       </c>
-      <c r="B30" s="39" t="s">
+      <c r="B30" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C30" s="39" t="s">
+      <c r="C30" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="D30" s="39">
+      <c r="D30" s="32">
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="E30" s="39"/>
-      <c r="F30" s="39">
+      <c r="E30" s="32"/>
+      <c r="F30" s="32">
         <v>31366</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="39">
+      <c r="A31" s="32">
         <v>176</v>
       </c>
-      <c r="B31" s="39" t="s">
+      <c r="B31" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="C31" s="39" t="s">
+      <c r="C31" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="39">
+      <c r="D31" s="32">
         <f t="shared" si="0"/>
         <v>176</v>
       </c>
-      <c r="E31" s="39"/>
-      <c r="F31" s="39">
+      <c r="E31" s="32"/>
+      <c r="F31" s="32">
         <v>31368</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="39">
+      <c r="A32" s="32">
         <v>659</v>
       </c>
-      <c r="B32" s="39" t="s">
+      <c r="B32" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="39" t="s">
+      <c r="C32" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="D32" s="39">
+      <c r="D32" s="32">
         <f t="shared" si="0"/>
         <v>659</v>
       </c>
-      <c r="E32" s="39"/>
-      <c r="F32" s="39">
+      <c r="E32" s="32"/>
+      <c r="F32" s="32">
         <v>31370</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="39">
+      <c r="A33" s="32">
         <v>183</v>
       </c>
-      <c r="B33" s="39" t="s">
+      <c r="B33" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="C33" s="39" t="s">
+      <c r="C33" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="D33" s="39">
+      <c r="D33" s="32">
         <f t="shared" si="0"/>
         <v>183</v>
       </c>
-      <c r="E33" s="39"/>
-      <c r="F33" s="39">
+      <c r="E33" s="32"/>
+      <c r="F33" s="32">
         <v>31377</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="39">
+      <c r="A34" s="32">
         <v>178</v>
       </c>
-      <c r="B34" s="39" t="s">
+      <c r="B34" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="C34" s="39" t="s">
+      <c r="C34" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="D34" s="39">
+      <c r="D34" s="32">
         <f t="shared" si="0"/>
         <v>178</v>
       </c>
-      <c r="E34" s="39"/>
-      <c r="F34" s="39">
+      <c r="E34" s="32"/>
+      <c r="F34" s="32">
         <v>31371</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="39">
+      <c r="A35" s="32">
         <v>179</v>
       </c>
-      <c r="B35" s="39" t="s">
+      <c r="B35" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="C35" s="39" t="s">
+      <c r="C35" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="D35" s="39">
+      <c r="D35" s="32">
         <f t="shared" si="0"/>
         <v>179</v>
       </c>
-      <c r="E35" s="39"/>
-      <c r="F35" s="39">
+      <c r="E35" s="32"/>
+      <c r="F35" s="32">
         <v>31372</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="39">
+      <c r="A36" s="32">
         <v>125</v>
       </c>
-      <c r="B36" s="39" t="s">
+      <c r="B36" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="C36" s="39" t="s">
+      <c r="C36" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="D36" s="39">
+      <c r="D36" s="32">
         <f t="shared" si="0"/>
         <v>125</v>
       </c>
-      <c r="E36" s="39"/>
-      <c r="F36" s="39">
+      <c r="E36" s="32"/>
+      <c r="F36" s="32">
         <v>31320</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="39">
+      <c r="A37" s="32">
         <v>127</v>
       </c>
-      <c r="B37" s="39" t="s">
+      <c r="B37" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="C37" s="39" t="s">
+      <c r="C37" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="D37" s="39">
+      <c r="D37" s="32">
         <f t="shared" si="0"/>
         <v>127</v>
       </c>
-      <c r="E37" s="39"/>
-      <c r="F37" s="39">
+      <c r="E37" s="32"/>
+      <c r="F37" s="32">
         <v>31012</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="39">
+      <c r="A38" s="32">
         <v>135</v>
       </c>
-      <c r="B38" s="39" t="s">
+      <c r="B38" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="C38" s="39" t="s">
+      <c r="C38" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="D38" s="39">
+      <c r="D38" s="32">
         <f t="shared" si="0"/>
         <v>135</v>
       </c>
-      <c r="E38" s="39"/>
-      <c r="F38" s="39">
+      <c r="E38" s="32"/>
+      <c r="F38" s="32">
         <v>31327</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="39">
+      <c r="A39" s="32">
         <v>142</v>
       </c>
-      <c r="B39" s="39" t="s">
+      <c r="B39" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="C39" s="39" t="s">
+      <c r="C39" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="D39" s="39">
+      <c r="D39" s="32">
         <f t="shared" si="0"/>
         <v>142</v>
       </c>
-      <c r="E39" s="39"/>
-      <c r="F39" s="39">
+      <c r="E39" s="32"/>
+      <c r="F39" s="32">
         <v>31333</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="39">
+      <c r="A40" s="32">
         <v>136</v>
       </c>
-      <c r="B40" s="39" t="s">
+      <c r="B40" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="C40" s="39" t="s">
+      <c r="C40" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="D40" s="39">
+      <c r="D40" s="32">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
-      <c r="E40" s="39"/>
-      <c r="F40" s="39">
+      <c r="E40" s="32"/>
+      <c r="F40" s="32">
         <v>31328</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="39">
+      <c r="A41" s="32">
         <v>181</v>
       </c>
-      <c r="B41" s="39" t="s">
+      <c r="B41" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="C41" s="39" t="s">
+      <c r="C41" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="D41" s="39">
+      <c r="D41" s="32">
         <f t="shared" si="0"/>
         <v>181</v>
       </c>
-      <c r="E41" s="39"/>
-      <c r="F41" s="39">
+      <c r="E41" s="32"/>
+      <c r="F41" s="32">
         <v>31375</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="39">
+      <c r="A42" s="32">
         <v>182</v>
       </c>
-      <c r="B42" s="39" t="s">
+      <c r="B42" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="C42" s="39" t="s">
+      <c r="C42" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="D42" s="39">
+      <c r="D42" s="32">
         <f t="shared" si="0"/>
         <v>182</v>
       </c>
-      <c r="E42" s="39"/>
-      <c r="F42" s="39">
+      <c r="E42" s="32"/>
+      <c r="F42" s="32">
         <v>31376</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="39">
+      <c r="A43" s="32">
         <v>184</v>
       </c>
-      <c r="B43" s="39" t="s">
+      <c r="B43" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="C43" s="39" t="s">
+      <c r="C43" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="D43" s="39">
+      <c r="D43" s="32">
         <f t="shared" si="0"/>
         <v>184</v>
       </c>
-      <c r="E43" s="39"/>
-      <c r="F43" s="39">
+      <c r="E43" s="32"/>
+      <c r="F43" s="32">
         <v>31378</v>
       </c>
     </row>
@@ -3672,2084 +3745,2084 @@
   <dimension ref="A1:F109"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" style="40" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.42578125" style="40" customWidth="1"/>
-    <col min="3" max="3" width="32" style="40" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="32.140625" style="40" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="30.7109375" style="40" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="40" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="40"/>
+    <col min="1" max="1" width="14.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" style="33" customWidth="1"/>
+    <col min="3" max="3" width="32" style="33" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="32.140625" style="33" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="30.7109375" style="33" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="33"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="30" t="s">
         <v>554</v>
       </c>
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="30" t="s">
         <v>553</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="30" t="s">
         <v>293</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="31" t="s">
         <v>485</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" s="30" t="s">
         <v>486</v>
       </c>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="31" t="s">
         <v>552</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="39">
+      <c r="A2" s="32">
         <v>823</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="39">
+      <c r="D2" s="32">
         <f>A2</f>
         <v>823</v>
       </c>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39">
+      <c r="E2" s="32"/>
+      <c r="F2" s="32">
         <v>313121</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="39">
+      <c r="A3" s="32">
         <v>852</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="C3" s="39" t="s">
+      <c r="C3" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="D3" s="39">
+      <c r="D3" s="32">
         <f t="shared" ref="D3:D66" si="0">A3</f>
         <v>852</v>
       </c>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39">
+      <c r="E3" s="32"/>
+      <c r="F3" s="32">
         <v>313130</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="39">
+      <c r="A4" s="32">
         <v>853</v>
       </c>
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="39">
+      <c r="D4" s="32">
         <f t="shared" si="0"/>
         <v>853</v>
       </c>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39">
+      <c r="E4" s="32"/>
+      <c r="F4" s="32">
         <v>313131</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="39">
+      <c r="A5" s="32">
         <v>858</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="C5" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="D5" s="39">
+      <c r="D5" s="32">
         <f t="shared" si="0"/>
         <v>858</v>
       </c>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39">
+      <c r="E5" s="32"/>
+      <c r="F5" s="32">
         <v>313136</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="39">
+      <c r="A6" s="32">
         <v>1587</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="39" t="s">
+      <c r="C6" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="D6" s="39">
+      <c r="D6" s="32">
         <f t="shared" si="0"/>
         <v>1587</v>
       </c>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39">
+      <c r="E6" s="32"/>
+      <c r="F6" s="32">
         <v>313142</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="39">
+      <c r="A7" s="32">
         <v>1599</v>
       </c>
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="C7" s="39" t="s">
+      <c r="C7" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="32">
         <f t="shared" si="0"/>
         <v>1599</v>
       </c>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39">
+      <c r="E7" s="32"/>
+      <c r="F7" s="32">
         <v>313147</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="39">
+      <c r="A8" s="32">
         <v>1589</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="C8" s="39" t="s">
+      <c r="C8" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="D8" s="39">
+      <c r="D8" s="32">
         <f t="shared" si="0"/>
         <v>1589</v>
       </c>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39">
+      <c r="E8" s="32"/>
+      <c r="F8" s="32">
         <v>313143</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="39">
+      <c r="A9" s="32">
         <v>909</v>
       </c>
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="32">
         <f t="shared" si="0"/>
         <v>909</v>
       </c>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39">
+      <c r="E9" s="32"/>
+      <c r="F9" s="32">
         <v>313217</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="39">
+      <c r="A10" s="32">
         <v>912</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="D10" s="39">
+      <c r="D10" s="32">
         <f t="shared" si="0"/>
         <v>912</v>
       </c>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39">
+      <c r="E10" s="32"/>
+      <c r="F10" s="32">
         <v>313220</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="39">
+      <c r="A11" s="32">
         <v>914</v>
       </c>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="D11" s="39">
+      <c r="D11" s="32">
         <f t="shared" si="0"/>
         <v>914</v>
       </c>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39">
+      <c r="E11" s="32"/>
+      <c r="F11" s="32">
         <v>313222</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="39">
+      <c r="A12" s="32">
         <v>915</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="32" t="s">
         <v>106</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="32" t="s">
         <v>107</v>
       </c>
-      <c r="D12" s="39">
+      <c r="D12" s="32">
         <f t="shared" si="0"/>
         <v>915</v>
       </c>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39">
+      <c r="E12" s="32"/>
+      <c r="F12" s="32">
         <v>313223</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="39">
+      <c r="A13" s="32">
         <v>916</v>
       </c>
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="D13" s="39">
+      <c r="D13" s="32">
         <f t="shared" si="0"/>
         <v>916</v>
       </c>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39">
+      <c r="E13" s="32"/>
+      <c r="F13" s="32">
         <v>313224</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="39">
+      <c r="A14" s="32">
         <v>920</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="D14" s="39">
+      <c r="D14" s="32">
         <f t="shared" si="0"/>
         <v>920</v>
       </c>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39">
+      <c r="E14" s="32"/>
+      <c r="F14" s="32">
         <v>313228</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="39">
+      <c r="A15" s="32">
         <v>921</v>
       </c>
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C15" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="D15" s="39">
+      <c r="D15" s="32">
         <f t="shared" si="0"/>
         <v>921</v>
       </c>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39">
+      <c r="E15" s="32"/>
+      <c r="F15" s="32">
         <v>313229</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="39">
+      <c r="A16" s="32">
         <v>924</v>
       </c>
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="C16" s="39" t="s">
+      <c r="C16" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="D16" s="39">
+      <c r="D16" s="32">
         <f t="shared" si="0"/>
         <v>924</v>
       </c>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39">
+      <c r="E16" s="32"/>
+      <c r="F16" s="32">
         <v>313232</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="39">
+      <c r="A17" s="32">
         <v>934</v>
       </c>
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="D17" s="39">
+      <c r="D17" s="32">
         <f t="shared" si="0"/>
         <v>934</v>
       </c>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39">
+      <c r="E17" s="32"/>
+      <c r="F17" s="32">
         <v>313233</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="39">
+      <c r="A18" s="32">
         <v>936</v>
       </c>
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="C18" s="39" t="s">
+      <c r="C18" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="D18" s="39">
+      <c r="D18" s="32">
         <f t="shared" si="0"/>
         <v>936</v>
       </c>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39">
+      <c r="E18" s="32"/>
+      <c r="F18" s="32">
         <v>313235</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="39">
+      <c r="A19" s="32">
         <v>938</v>
       </c>
-      <c r="B19" s="39" t="s">
+      <c r="B19" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="C19" s="39" t="s">
+      <c r="C19" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="D19" s="39">
+      <c r="D19" s="32">
         <f t="shared" si="0"/>
         <v>938</v>
       </c>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39">
+      <c r="E19" s="32"/>
+      <c r="F19" s="32">
         <v>313237</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="39">
+      <c r="A20" s="32">
         <v>951</v>
       </c>
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="C20" s="39" t="s">
+      <c r="C20" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="D20" s="39">
+      <c r="D20" s="32">
         <f t="shared" si="0"/>
         <v>951</v>
       </c>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39">
+      <c r="E20" s="32"/>
+      <c r="F20" s="32">
         <v>313249</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="39">
+      <c r="A21" s="32">
         <v>952</v>
       </c>
-      <c r="B21" s="39" t="s">
+      <c r="B21" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="C21" s="39" t="s">
+      <c r="C21" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="D21" s="39">
+      <c r="D21" s="32">
         <f t="shared" si="0"/>
         <v>952</v>
       </c>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39">
+      <c r="E21" s="32"/>
+      <c r="F21" s="32">
         <v>313250</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="39">
+      <c r="A22" s="32">
         <v>960</v>
       </c>
-      <c r="B22" s="39" t="s">
+      <c r="B22" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="C22" s="39" t="s">
+      <c r="C22" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="D22" s="39">
+      <c r="D22" s="32">
         <f t="shared" si="0"/>
         <v>960</v>
       </c>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39">
+      <c r="E22" s="32"/>
+      <c r="F22" s="32">
         <v>313257</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="39">
+      <c r="A23" s="32">
         <v>967</v>
       </c>
-      <c r="B23" s="39" t="s">
+      <c r="B23" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="C23" s="39" t="s">
+      <c r="C23" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="D23" s="39">
+      <c r="D23" s="32">
         <f t="shared" si="0"/>
         <v>967</v>
       </c>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39">
+      <c r="E23" s="32"/>
+      <c r="F23" s="32">
         <v>313263</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="39">
+      <c r="A24" s="32">
         <v>969</v>
       </c>
-      <c r="B24" s="39" t="s">
+      <c r="B24" s="32" t="s">
         <v>130</v>
       </c>
-      <c r="C24" s="39" t="s">
+      <c r="C24" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="D24" s="39">
+      <c r="D24" s="32">
         <f t="shared" si="0"/>
         <v>969</v>
       </c>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39">
+      <c r="E24" s="32"/>
+      <c r="F24" s="32">
         <v>313265</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="39">
+      <c r="A25" s="32">
         <v>973</v>
       </c>
-      <c r="B25" s="39" t="s">
+      <c r="B25" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="C25" s="39" t="s">
+      <c r="C25" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="D25" s="39">
+      <c r="D25" s="32">
         <f t="shared" si="0"/>
         <v>973</v>
       </c>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39">
+      <c r="E25" s="32"/>
+      <c r="F25" s="32">
         <v>313270</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="39">
+      <c r="A26" s="32">
         <v>965</v>
       </c>
-      <c r="B26" s="39" t="s">
+      <c r="B26" s="32" t="s">
         <v>134</v>
       </c>
-      <c r="C26" s="39" t="s">
+      <c r="C26" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="39">
+      <c r="D26" s="32">
         <f t="shared" si="0"/>
         <v>965</v>
       </c>
-      <c r="E26" s="39"/>
-      <c r="F26" s="39">
+      <c r="E26" s="32"/>
+      <c r="F26" s="32">
         <v>313269</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="39">
+      <c r="A27" s="32">
         <v>979</v>
       </c>
-      <c r="B27" s="39" t="s">
+      <c r="B27" s="32" t="s">
         <v>136</v>
       </c>
-      <c r="C27" s="39" t="s">
+      <c r="C27" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="D27" s="39">
+      <c r="D27" s="32">
         <f t="shared" si="0"/>
         <v>979</v>
       </c>
-      <c r="E27" s="39"/>
-      <c r="F27" s="39">
+      <c r="E27" s="32"/>
+      <c r="F27" s="32">
         <v>313276</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="39">
+      <c r="A28" s="32">
         <v>981</v>
       </c>
-      <c r="B28" s="39" t="s">
+      <c r="B28" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="C28" s="39" t="s">
+      <c r="C28" s="32" t="s">
         <v>139</v>
       </c>
-      <c r="D28" s="39">
+      <c r="D28" s="32">
         <f t="shared" si="0"/>
         <v>981</v>
       </c>
-      <c r="E28" s="39"/>
-      <c r="F28" s="39">
+      <c r="E28" s="32"/>
+      <c r="F28" s="32">
         <v>313278</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="39">
+      <c r="A29" s="32">
         <v>985</v>
       </c>
-      <c r="B29" s="39" t="s">
+      <c r="B29" s="32" t="s">
         <v>140</v>
       </c>
-      <c r="C29" s="39" t="s">
+      <c r="C29" s="32" t="s">
         <v>141</v>
       </c>
-      <c r="D29" s="39">
+      <c r="D29" s="32">
         <f t="shared" si="0"/>
         <v>985</v>
       </c>
-      <c r="E29" s="39"/>
-      <c r="F29" s="39">
+      <c r="E29" s="32"/>
+      <c r="F29" s="32">
         <v>313282</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="39">
+      <c r="A30" s="32">
         <v>987</v>
       </c>
-      <c r="B30" s="39" t="s">
+      <c r="B30" s="32" t="s">
         <v>142</v>
       </c>
-      <c r="C30" s="39" t="s">
+      <c r="C30" s="32" t="s">
         <v>143</v>
       </c>
-      <c r="D30" s="39">
+      <c r="D30" s="32">
         <f t="shared" si="0"/>
         <v>987</v>
       </c>
-      <c r="E30" s="39"/>
-      <c r="F30" s="39">
+      <c r="E30" s="32"/>
+      <c r="F30" s="32">
         <v>313284</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="39">
+      <c r="A31" s="32">
         <v>994</v>
       </c>
-      <c r="B31" s="39" t="s">
+      <c r="B31" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="C31" s="39" t="s">
+      <c r="C31" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="D31" s="39">
+      <c r="D31" s="32">
         <f t="shared" si="0"/>
         <v>994</v>
       </c>
-      <c r="E31" s="39"/>
-      <c r="F31" s="39">
+      <c r="E31" s="32"/>
+      <c r="F31" s="32">
         <v>310200</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="39">
+      <c r="A32" s="32">
         <v>996</v>
       </c>
-      <c r="B32" s="39" t="s">
+      <c r="B32" s="32" t="s">
         <v>146</v>
       </c>
-      <c r="C32" s="39" t="s">
+      <c r="C32" s="32" t="s">
         <v>147</v>
       </c>
-      <c r="D32" s="39">
+      <c r="D32" s="32">
         <f t="shared" si="0"/>
         <v>996</v>
       </c>
-      <c r="E32" s="39"/>
-      <c r="F32" s="39">
+      <c r="E32" s="32"/>
+      <c r="F32" s="32">
         <v>310202</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="39">
+      <c r="A33" s="32">
         <v>999</v>
       </c>
-      <c r="B33" s="39" t="s">
+      <c r="B33" s="32" t="s">
         <v>148</v>
       </c>
-      <c r="C33" s="39" t="s">
+      <c r="C33" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="D33" s="39">
+      <c r="D33" s="32">
         <f t="shared" si="0"/>
         <v>999</v>
       </c>
-      <c r="E33" s="39"/>
-      <c r="F33" s="39">
+      <c r="E33" s="32"/>
+      <c r="F33" s="32">
         <v>310205</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="39">
+      <c r="A34" s="32">
         <v>1000</v>
       </c>
-      <c r="B34" s="39" t="s">
+      <c r="B34" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="C34" s="39" t="s">
+      <c r="C34" s="32" t="s">
         <v>151</v>
       </c>
-      <c r="D34" s="39">
+      <c r="D34" s="32">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="E34" s="39"/>
-      <c r="F34" s="39">
+      <c r="E34" s="32"/>
+      <c r="F34" s="32">
         <v>310206</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="39">
+      <c r="A35" s="32">
         <v>1009</v>
       </c>
-      <c r="B35" s="39" t="s">
+      <c r="B35" s="32" t="s">
         <v>152</v>
       </c>
-      <c r="C35" s="39" t="s">
+      <c r="C35" s="32" t="s">
         <v>153</v>
       </c>
-      <c r="D35" s="39">
+      <c r="D35" s="32">
         <f t="shared" si="0"/>
         <v>1009</v>
       </c>
-      <c r="E35" s="39"/>
-      <c r="F35" s="39">
+      <c r="E35" s="32"/>
+      <c r="F35" s="32">
         <v>310213</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="39">
+      <c r="A36" s="32">
         <v>1012</v>
       </c>
-      <c r="B36" s="39" t="s">
+      <c r="B36" s="32" t="s">
         <v>154</v>
       </c>
-      <c r="C36" s="39" t="s">
+      <c r="C36" s="32" t="s">
         <v>155</v>
       </c>
-      <c r="D36" s="39">
+      <c r="D36" s="32">
         <f t="shared" si="0"/>
         <v>1012</v>
       </c>
-      <c r="E36" s="39"/>
-      <c r="F36" s="39">
+      <c r="E36" s="32"/>
+      <c r="F36" s="32">
         <v>310215</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="39">
+      <c r="A37" s="32">
         <v>1015</v>
       </c>
-      <c r="B37" s="39" t="s">
+      <c r="B37" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="C37" s="39" t="s">
+      <c r="C37" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="D37" s="39">
+      <c r="D37" s="32">
         <f t="shared" si="0"/>
         <v>1015</v>
       </c>
-      <c r="E37" s="39"/>
-      <c r="F37" s="39">
+      <c r="E37" s="32"/>
+      <c r="F37" s="32">
         <v>310218</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="39">
+      <c r="A38" s="32">
         <v>1016</v>
       </c>
-      <c r="B38" s="39" t="s">
+      <c r="B38" s="32" t="s">
         <v>158</v>
       </c>
-      <c r="C38" s="39" t="s">
+      <c r="C38" s="32" t="s">
         <v>159</v>
       </c>
-      <c r="D38" s="39">
+      <c r="D38" s="32">
         <f t="shared" si="0"/>
         <v>1016</v>
       </c>
-      <c r="E38" s="39"/>
-      <c r="F38" s="39">
+      <c r="E38" s="32"/>
+      <c r="F38" s="32">
         <v>310219</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="39">
+      <c r="A39" s="32">
         <v>1056</v>
       </c>
-      <c r="B39" s="39" t="s">
+      <c r="B39" s="32" t="s">
         <v>160</v>
       </c>
-      <c r="C39" s="39" t="s">
+      <c r="C39" s="32" t="s">
         <v>161</v>
       </c>
-      <c r="D39" s="39">
+      <c r="D39" s="32">
         <f t="shared" si="0"/>
         <v>1056</v>
       </c>
-      <c r="E39" s="39"/>
-      <c r="F39" s="39">
+      <c r="E39" s="32"/>
+      <c r="F39" s="32">
         <v>313324</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="39">
+      <c r="A40" s="32">
         <v>1065</v>
       </c>
-      <c r="B40" s="39" t="s">
+      <c r="B40" s="32" t="s">
         <v>162</v>
       </c>
-      <c r="C40" s="39" t="s">
+      <c r="C40" s="32" t="s">
         <v>163</v>
       </c>
-      <c r="D40" s="39">
+      <c r="D40" s="32">
         <f t="shared" si="0"/>
         <v>1065</v>
       </c>
-      <c r="E40" s="39"/>
-      <c r="F40" s="39">
+      <c r="E40" s="32"/>
+      <c r="F40" s="32">
         <v>313332</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="39">
+      <c r="A41" s="32">
         <v>1067</v>
       </c>
-      <c r="B41" s="39" t="s">
+      <c r="B41" s="32" t="s">
         <v>164</v>
       </c>
-      <c r="C41" s="39" t="s">
+      <c r="C41" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="D41" s="39">
+      <c r="D41" s="32">
         <f t="shared" si="0"/>
         <v>1067</v>
       </c>
-      <c r="E41" s="39"/>
-      <c r="F41" s="39">
+      <c r="E41" s="32"/>
+      <c r="F41" s="32">
         <v>313333</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="39">
+      <c r="A42" s="32">
         <v>1074</v>
       </c>
-      <c r="B42" s="39" t="s">
+      <c r="B42" s="32" t="s">
         <v>166</v>
       </c>
-      <c r="C42" s="39" t="s">
+      <c r="C42" s="32" t="s">
         <v>167</v>
       </c>
-      <c r="D42" s="39">
+      <c r="D42" s="32">
         <f t="shared" si="0"/>
         <v>1074</v>
       </c>
-      <c r="E42" s="39"/>
-      <c r="F42" s="39">
+      <c r="E42" s="32"/>
+      <c r="F42" s="32">
         <v>313337</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="39">
+      <c r="A43" s="32">
         <v>1100</v>
       </c>
-      <c r="B43" s="39" t="s">
+      <c r="B43" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="C43" s="39" t="s">
+      <c r="C43" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="D43" s="39">
+      <c r="D43" s="32">
         <f t="shared" si="0"/>
         <v>1100</v>
       </c>
-      <c r="E43" s="39"/>
-      <c r="F43" s="39">
+      <c r="E43" s="32"/>
+      <c r="F43" s="32">
         <v>313351</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="39">
+      <c r="A44" s="32">
         <v>1101</v>
       </c>
-      <c r="B44" s="39" t="s">
+      <c r="B44" s="32" t="s">
         <v>170</v>
       </c>
-      <c r="C44" s="39" t="s">
+      <c r="C44" s="32" t="s">
         <v>171</v>
       </c>
-      <c r="D44" s="39">
+      <c r="D44" s="32">
         <f t="shared" si="0"/>
         <v>1101</v>
       </c>
-      <c r="E44" s="39"/>
-      <c r="F44" s="39">
+      <c r="E44" s="32"/>
+      <c r="F44" s="32">
         <v>313352</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="39">
+      <c r="A45" s="32">
         <v>1150</v>
       </c>
-      <c r="B45" s="39" t="s">
+      <c r="B45" s="32" t="s">
         <v>172</v>
       </c>
-      <c r="C45" s="39" t="s">
+      <c r="C45" s="32" t="s">
         <v>173</v>
       </c>
-      <c r="D45" s="39">
+      <c r="D45" s="32">
         <f t="shared" si="0"/>
         <v>1150</v>
       </c>
-      <c r="E45" s="39"/>
-      <c r="F45" s="39">
+      <c r="E45" s="32"/>
+      <c r="F45" s="32">
         <v>313397</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="39">
+      <c r="A46" s="32">
         <v>1151</v>
       </c>
-      <c r="B46" s="39" t="s">
+      <c r="B46" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="C46" s="39" t="s">
+      <c r="C46" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="D46" s="39">
+      <c r="D46" s="32">
         <f t="shared" si="0"/>
         <v>1151</v>
       </c>
-      <c r="E46" s="39"/>
-      <c r="F46" s="39">
+      <c r="E46" s="32"/>
+      <c r="F46" s="32">
         <v>313398</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="39">
+      <c r="A47" s="32">
         <v>1139</v>
       </c>
-      <c r="B47" s="39" t="s">
+      <c r="B47" s="32" t="s">
         <v>176</v>
       </c>
-      <c r="C47" s="39" t="s">
+      <c r="C47" s="32" t="s">
         <v>177</v>
       </c>
-      <c r="D47" s="39">
+      <c r="D47" s="32">
         <f t="shared" si="0"/>
         <v>1139</v>
       </c>
-      <c r="E47" s="39"/>
-      <c r="F47" s="39">
+      <c r="E47" s="32"/>
+      <c r="F47" s="32">
         <v>313386</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="39">
+      <c r="A48" s="32">
         <v>1145</v>
       </c>
-      <c r="B48" s="39" t="s">
+      <c r="B48" s="32" t="s">
         <v>178</v>
       </c>
-      <c r="C48" s="39" t="s">
+      <c r="C48" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="D48" s="39">
+      <c r="D48" s="32">
         <f t="shared" si="0"/>
         <v>1145</v>
       </c>
-      <c r="E48" s="39"/>
-      <c r="F48" s="39">
+      <c r="E48" s="32"/>
+      <c r="F48" s="32">
         <v>313392</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="39">
+      <c r="A49" s="32">
         <v>1147</v>
       </c>
-      <c r="B49" s="39" t="s">
+      <c r="B49" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="C49" s="39" t="s">
+      <c r="C49" s="32" t="s">
         <v>181</v>
       </c>
-      <c r="D49" s="39">
+      <c r="D49" s="32">
         <f t="shared" si="0"/>
         <v>1147</v>
       </c>
-      <c r="E49" s="39"/>
-      <c r="F49" s="39">
+      <c r="E49" s="32"/>
+      <c r="F49" s="32">
         <v>313394</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="39">
+      <c r="A50" s="32">
         <v>1148</v>
       </c>
-      <c r="B50" s="39" t="s">
+      <c r="B50" s="32" t="s">
         <v>182</v>
       </c>
-      <c r="C50" s="39" t="s">
+      <c r="C50" s="32" t="s">
         <v>183</v>
       </c>
-      <c r="D50" s="39">
+      <c r="D50" s="32">
         <f t="shared" si="0"/>
         <v>1148</v>
       </c>
-      <c r="E50" s="39"/>
-      <c r="F50" s="39">
+      <c r="E50" s="32"/>
+      <c r="F50" s="32">
         <v>313395</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="39">
+      <c r="A51" s="32">
         <v>1153</v>
       </c>
-      <c r="B51" s="39" t="s">
+      <c r="B51" s="32" t="s">
         <v>184</v>
       </c>
-      <c r="C51" s="39" t="s">
+      <c r="C51" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="D51" s="39">
+      <c r="D51" s="32">
         <f t="shared" si="0"/>
         <v>1153</v>
       </c>
-      <c r="E51" s="39"/>
-      <c r="F51" s="39">
+      <c r="E51" s="32"/>
+      <c r="F51" s="32">
         <v>313400</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="39">
+      <c r="A52" s="32">
         <v>1164</v>
       </c>
-      <c r="B52" s="39" t="s">
+      <c r="B52" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="C52" s="39" t="s">
+      <c r="C52" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="D52" s="39">
+      <c r="D52" s="32">
         <f t="shared" si="0"/>
         <v>1164</v>
       </c>
-      <c r="E52" s="39"/>
-      <c r="F52" s="39">
+      <c r="E52" s="32"/>
+      <c r="F52" s="32">
         <v>313411</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="39">
+      <c r="A53" s="32">
         <v>1166</v>
       </c>
-      <c r="B53" s="39" t="s">
+      <c r="B53" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="C53" s="39" t="s">
+      <c r="C53" s="32" t="s">
         <v>189</v>
       </c>
-      <c r="D53" s="39">
+      <c r="D53" s="32">
         <f t="shared" si="0"/>
         <v>1166</v>
       </c>
-      <c r="E53" s="39"/>
-      <c r="F53" s="39">
+      <c r="E53" s="32"/>
+      <c r="F53" s="32">
         <v>313413</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="39">
+      <c r="A54" s="32">
         <v>1169</v>
       </c>
-      <c r="B54" s="39" t="s">
+      <c r="B54" s="32" t="s">
         <v>190</v>
       </c>
-      <c r="C54" s="39" t="s">
+      <c r="C54" s="32" t="s">
         <v>191</v>
       </c>
-      <c r="D54" s="39">
+      <c r="D54" s="32">
         <f t="shared" si="0"/>
         <v>1169</v>
       </c>
-      <c r="E54" s="39"/>
-      <c r="F54" s="39">
+      <c r="E54" s="32"/>
+      <c r="F54" s="32">
         <v>313416</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="39">
+      <c r="A55" s="32">
         <v>1173</v>
       </c>
-      <c r="B55" s="39" t="s">
+      <c r="B55" s="32" t="s">
         <v>192</v>
       </c>
-      <c r="C55" s="39" t="s">
+      <c r="C55" s="32" t="s">
         <v>193</v>
       </c>
-      <c r="D55" s="39">
+      <c r="D55" s="32">
         <f t="shared" si="0"/>
         <v>1173</v>
       </c>
-      <c r="E55" s="39"/>
-      <c r="F55" s="39">
+      <c r="E55" s="32"/>
+      <c r="F55" s="32">
         <v>313421</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="39">
+      <c r="A56" s="32">
         <v>1174</v>
       </c>
-      <c r="B56" s="39" t="s">
+      <c r="B56" s="32" t="s">
         <v>194</v>
       </c>
-      <c r="C56" s="39" t="s">
+      <c r="C56" s="32" t="s">
         <v>195</v>
       </c>
-      <c r="D56" s="39">
+      <c r="D56" s="32">
         <f t="shared" si="0"/>
         <v>1174</v>
       </c>
-      <c r="E56" s="39"/>
-      <c r="F56" s="39">
+      <c r="E56" s="32"/>
+      <c r="F56" s="32">
         <v>313422</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="39">
+      <c r="A57" s="32">
         <v>1209</v>
       </c>
-      <c r="B57" s="39" t="s">
+      <c r="B57" s="32" t="s">
         <v>196</v>
       </c>
-      <c r="C57" s="39" t="s">
+      <c r="C57" s="32" t="s">
         <v>197</v>
       </c>
-      <c r="D57" s="39">
+      <c r="D57" s="32">
         <f t="shared" si="0"/>
         <v>1209</v>
       </c>
-      <c r="E57" s="39"/>
-      <c r="F57" s="39">
+      <c r="E57" s="32"/>
+      <c r="F57" s="32">
         <v>313461</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="39">
+      <c r="A58" s="32">
         <v>1215</v>
       </c>
-      <c r="B58" s="39" t="s">
+      <c r="B58" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="C58" s="39" t="s">
+      <c r="C58" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="D58" s="39">
+      <c r="D58" s="32">
         <f t="shared" si="0"/>
         <v>1215</v>
       </c>
-      <c r="E58" s="39"/>
-      <c r="F58" s="39">
+      <c r="E58" s="32"/>
+      <c r="F58" s="32">
         <v>313474</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="39">
+      <c r="A59" s="32">
         <v>1222</v>
       </c>
-      <c r="B59" s="39" t="s">
+      <c r="B59" s="32" t="s">
         <v>198</v>
       </c>
-      <c r="C59" s="39" t="s">
+      <c r="C59" s="32" t="s">
         <v>199</v>
       </c>
-      <c r="D59" s="39">
+      <c r="D59" s="32">
         <f t="shared" si="0"/>
         <v>1222</v>
       </c>
-      <c r="E59" s="39"/>
-      <c r="F59" s="39">
+      <c r="E59" s="32"/>
+      <c r="F59" s="32">
         <v>313481</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="39">
+      <c r="A60" s="32">
         <v>1232</v>
       </c>
-      <c r="B60" s="39" t="s">
+      <c r="B60" s="32" t="s">
         <v>200</v>
       </c>
-      <c r="C60" s="39" t="s">
+      <c r="C60" s="32" t="s">
         <v>201</v>
       </c>
-      <c r="D60" s="39">
+      <c r="D60" s="32">
         <f t="shared" si="0"/>
         <v>1232</v>
       </c>
-      <c r="E60" s="39"/>
-      <c r="F60" s="39">
+      <c r="E60" s="32"/>
+      <c r="F60" s="32">
         <v>313491</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="39">
+      <c r="A61" s="32">
         <v>1238</v>
       </c>
-      <c r="B61" s="39" t="s">
+      <c r="B61" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="C61" s="39" t="s">
+      <c r="C61" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="D61" s="39">
+      <c r="D61" s="32">
         <f t="shared" si="0"/>
         <v>1238</v>
       </c>
-      <c r="E61" s="39"/>
-      <c r="F61" s="39">
+      <c r="E61" s="32"/>
+      <c r="F61" s="32">
         <v>313497</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="39">
+      <c r="A62" s="32">
         <v>1064</v>
       </c>
-      <c r="B62" s="39" t="s">
+      <c r="B62" s="32" t="s">
         <v>202</v>
       </c>
-      <c r="C62" s="39" t="s">
+      <c r="C62" s="32" t="s">
         <v>203</v>
       </c>
-      <c r="D62" s="39">
+      <c r="D62" s="32">
         <f t="shared" si="0"/>
         <v>1064</v>
       </c>
-      <c r="E62" s="39"/>
-      <c r="F62" s="39">
+      <c r="E62" s="32"/>
+      <c r="F62" s="32">
         <v>313531</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="39">
+      <c r="A63" s="32">
         <v>1066</v>
       </c>
-      <c r="B63" s="39" t="s">
+      <c r="B63" s="32" t="s">
         <v>204</v>
       </c>
-      <c r="C63" s="39" t="s">
+      <c r="C63" s="32" t="s">
         <v>205</v>
       </c>
-      <c r="D63" s="39">
+      <c r="D63" s="32">
         <f t="shared" si="0"/>
         <v>1066</v>
       </c>
-      <c r="E63" s="39"/>
-      <c r="F63" s="39">
+      <c r="E63" s="32"/>
+      <c r="F63" s="32">
         <v>313532</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="39">
+      <c r="A64" s="32">
         <v>1077</v>
       </c>
-      <c r="B64" s="39" t="s">
+      <c r="B64" s="32" t="s">
         <v>206</v>
       </c>
-      <c r="C64" s="39" t="s">
+      <c r="C64" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="D64" s="39">
+      <c r="D64" s="32">
         <f t="shared" si="0"/>
         <v>1077</v>
       </c>
-      <c r="E64" s="39"/>
-      <c r="F64" s="39">
+      <c r="E64" s="32"/>
+      <c r="F64" s="32">
         <v>313537</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="39">
+      <c r="A65" s="32">
         <v>1288</v>
       </c>
-      <c r="B65" s="39" t="s">
+      <c r="B65" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="C65" s="39" t="s">
+      <c r="C65" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="D65" s="39">
+      <c r="D65" s="32">
         <f t="shared" si="0"/>
         <v>1288</v>
       </c>
-      <c r="E65" s="39"/>
-      <c r="F65" s="39">
+      <c r="E65" s="32"/>
+      <c r="F65" s="32">
         <v>313540</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="39">
+      <c r="A66" s="32">
         <v>1289</v>
       </c>
-      <c r="B66" s="39" t="s">
+      <c r="B66" s="32" t="s">
         <v>208</v>
       </c>
-      <c r="C66" s="39" t="s">
+      <c r="C66" s="32" t="s">
         <v>209</v>
       </c>
-      <c r="D66" s="39">
+      <c r="D66" s="32">
         <f t="shared" si="0"/>
         <v>1289</v>
       </c>
-      <c r="E66" s="39"/>
-      <c r="F66" s="39">
+      <c r="E66" s="32"/>
+      <c r="F66" s="32">
         <v>313541</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="39">
+      <c r="A67" s="32">
         <v>1294</v>
       </c>
-      <c r="B67" s="39" t="s">
+      <c r="B67" s="32" t="s">
         <v>210</v>
       </c>
-      <c r="C67" s="39" t="s">
+      <c r="C67" s="32" t="s">
         <v>211</v>
       </c>
-      <c r="D67" s="39">
+      <c r="D67" s="32">
         <f t="shared" ref="D67:D109" si="1">A67</f>
         <v>1294</v>
       </c>
-      <c r="E67" s="39"/>
-      <c r="F67" s="39">
+      <c r="E67" s="32"/>
+      <c r="F67" s="32">
         <v>313546</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="39">
+      <c r="A68" s="32">
         <v>1297</v>
       </c>
-      <c r="B68" s="39" t="s">
+      <c r="B68" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="C68" s="39" t="s">
+      <c r="C68" s="32" t="s">
         <v>213</v>
       </c>
-      <c r="D68" s="39">
+      <c r="D68" s="32">
         <f t="shared" si="1"/>
         <v>1297</v>
       </c>
-      <c r="E68" s="39"/>
-      <c r="F68" s="39">
+      <c r="E68" s="32"/>
+      <c r="F68" s="32">
         <v>313549</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="39">
+      <c r="A69" s="32">
         <v>1298</v>
       </c>
-      <c r="B69" s="39" t="s">
+      <c r="B69" s="32" t="s">
         <v>214</v>
       </c>
-      <c r="C69" s="39" t="s">
+      <c r="C69" s="32" t="s">
         <v>215</v>
       </c>
-      <c r="D69" s="39">
+      <c r="D69" s="32">
         <f t="shared" si="1"/>
         <v>1298</v>
       </c>
-      <c r="E69" s="39"/>
-      <c r="F69" s="39">
+      <c r="E69" s="32"/>
+      <c r="F69" s="32">
         <v>313550</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="39">
+      <c r="A70" s="32">
         <v>1308</v>
       </c>
-      <c r="B70" s="39" t="s">
+      <c r="B70" s="32" t="s">
         <v>216</v>
       </c>
-      <c r="C70" s="39" t="s">
+      <c r="C70" s="32" t="s">
         <v>217</v>
       </c>
-      <c r="D70" s="39">
+      <c r="D70" s="32">
         <f t="shared" si="1"/>
         <v>1308</v>
       </c>
-      <c r="E70" s="39"/>
-      <c r="F70" s="39">
+      <c r="E70" s="32"/>
+      <c r="F70" s="32">
         <v>313560</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="39">
+      <c r="A71" s="32">
         <v>1322</v>
       </c>
-      <c r="B71" s="39" t="s">
+      <c r="B71" s="32" t="s">
         <v>218</v>
       </c>
-      <c r="C71" s="39" t="s">
+      <c r="C71" s="32" t="s">
         <v>219</v>
       </c>
-      <c r="D71" s="39">
+      <c r="D71" s="32">
         <f t="shared" si="1"/>
         <v>1322</v>
       </c>
-      <c r="E71" s="39"/>
-      <c r="F71" s="39">
+      <c r="E71" s="32"/>
+      <c r="F71" s="32">
         <v>313574</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="39">
+      <c r="A72" s="32">
         <v>1326</v>
       </c>
-      <c r="B72" s="39" t="s">
+      <c r="B72" s="32" t="s">
         <v>220</v>
       </c>
-      <c r="C72" s="39" t="s">
+      <c r="C72" s="32" t="s">
         <v>221</v>
       </c>
-      <c r="D72" s="39">
+      <c r="D72" s="32">
         <f t="shared" si="1"/>
         <v>1326</v>
       </c>
-      <c r="E72" s="39"/>
-      <c r="F72" s="39">
+      <c r="E72" s="32"/>
+      <c r="F72" s="32">
         <v>313578</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="39">
+      <c r="A73" s="32">
         <v>1358</v>
       </c>
-      <c r="B73" s="39" t="s">
+      <c r="B73" s="32" t="s">
         <v>222</v>
       </c>
-      <c r="C73" s="39" t="s">
+      <c r="C73" s="32" t="s">
         <v>223</v>
       </c>
-      <c r="D73" s="39">
+      <c r="D73" s="32">
         <f t="shared" si="1"/>
         <v>1358</v>
       </c>
-      <c r="E73" s="39"/>
-      <c r="F73" s="39">
+      <c r="E73" s="32"/>
+      <c r="F73" s="32">
         <v>313603</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="39">
+      <c r="A74" s="32">
         <v>1348</v>
       </c>
-      <c r="B74" s="39" t="s">
+      <c r="B74" s="32" t="s">
         <v>224</v>
       </c>
-      <c r="C74" s="39" t="s">
+      <c r="C74" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="D74" s="39">
+      <c r="D74" s="32">
         <f t="shared" si="1"/>
         <v>1348</v>
       </c>
-      <c r="E74" s="39"/>
-      <c r="F74" s="39">
+      <c r="E74" s="32"/>
+      <c r="F74" s="32">
         <v>313593</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="39">
+      <c r="A75" s="32">
         <v>1349</v>
       </c>
-      <c r="B75" s="39" t="s">
+      <c r="B75" s="32" t="s">
         <v>225</v>
       </c>
-      <c r="C75" s="39" t="s">
+      <c r="C75" s="32" t="s">
         <v>226</v>
       </c>
-      <c r="D75" s="39">
+      <c r="D75" s="32">
         <f t="shared" si="1"/>
         <v>1349</v>
       </c>
-      <c r="E75" s="39"/>
-      <c r="F75" s="39">
+      <c r="E75" s="32"/>
+      <c r="F75" s="32">
         <v>313594</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="39">
+      <c r="A76" s="32">
         <v>1350</v>
       </c>
-      <c r="B76" s="39" t="s">
+      <c r="B76" s="32" t="s">
         <v>227</v>
       </c>
-      <c r="C76" s="39" t="s">
+      <c r="C76" s="32" t="s">
         <v>228</v>
       </c>
-      <c r="D76" s="39">
+      <c r="D76" s="32">
         <f t="shared" si="1"/>
         <v>1350</v>
       </c>
-      <c r="E76" s="39"/>
-      <c r="F76" s="39">
+      <c r="E76" s="32"/>
+      <c r="F76" s="32">
         <v>313595</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="39">
+      <c r="A77" s="32">
         <v>1351</v>
       </c>
-      <c r="B77" s="39" t="s">
+      <c r="B77" s="32" t="s">
         <v>229</v>
       </c>
-      <c r="C77" s="39" t="s">
+      <c r="C77" s="32" t="s">
         <v>230</v>
       </c>
-      <c r="D77" s="39">
+      <c r="D77" s="32">
         <f t="shared" si="1"/>
         <v>1351</v>
       </c>
-      <c r="E77" s="39"/>
-      <c r="F77" s="39">
+      <c r="E77" s="32"/>
+      <c r="F77" s="32">
         <v>313596</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="39">
+      <c r="A78" s="32">
         <v>1352</v>
       </c>
-      <c r="B78" s="39" t="s">
+      <c r="B78" s="32" t="s">
         <v>231</v>
       </c>
-      <c r="C78" s="39" t="s">
+      <c r="C78" s="32" t="s">
         <v>232</v>
       </c>
-      <c r="D78" s="39">
+      <c r="D78" s="32">
         <f t="shared" si="1"/>
         <v>1352</v>
       </c>
-      <c r="E78" s="39"/>
-      <c r="F78" s="39">
+      <c r="E78" s="32"/>
+      <c r="F78" s="32">
         <v>313597</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="39">
+      <c r="A79" s="32">
         <v>1353</v>
       </c>
-      <c r="B79" s="39" t="s">
+      <c r="B79" s="32" t="s">
         <v>233</v>
       </c>
-      <c r="C79" s="39" t="s">
+      <c r="C79" s="32" t="s">
         <v>234</v>
       </c>
-      <c r="D79" s="39">
+      <c r="D79" s="32">
         <f t="shared" si="1"/>
         <v>1353</v>
       </c>
-      <c r="E79" s="39"/>
-      <c r="F79" s="39">
+      <c r="E79" s="32"/>
+      <c r="F79" s="32">
         <v>313598</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="39">
+      <c r="A80" s="32">
         <v>1401</v>
       </c>
-      <c r="B80" s="39" t="s">
+      <c r="B80" s="32" t="s">
         <v>235</v>
       </c>
-      <c r="C80" s="39" t="s">
+      <c r="C80" s="32" t="s">
         <v>236</v>
       </c>
-      <c r="D80" s="39">
+      <c r="D80" s="32">
         <f t="shared" si="1"/>
         <v>1401</v>
       </c>
-      <c r="E80" s="39"/>
-      <c r="F80" s="39">
+      <c r="E80" s="32"/>
+      <c r="F80" s="32">
         <v>313647</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="39">
+      <c r="A81" s="32">
         <v>1406</v>
       </c>
-      <c r="B81" s="39" t="s">
+      <c r="B81" s="32" t="s">
         <v>237</v>
       </c>
-      <c r="C81" s="39" t="s">
+      <c r="C81" s="32" t="s">
         <v>238</v>
       </c>
-      <c r="D81" s="39">
+      <c r="D81" s="32">
         <f t="shared" si="1"/>
         <v>1406</v>
       </c>
-      <c r="E81" s="39"/>
-      <c r="F81" s="39">
+      <c r="E81" s="32"/>
+      <c r="F81" s="32">
         <v>313646</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="39">
+      <c r="A82" s="32">
         <v>1408</v>
       </c>
-      <c r="B82" s="39" t="s">
+      <c r="B82" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="C82" s="39" t="s">
+      <c r="C82" s="32" t="s">
         <v>240</v>
       </c>
-      <c r="D82" s="39">
+      <c r="D82" s="32">
         <f t="shared" si="1"/>
         <v>1408</v>
       </c>
-      <c r="E82" s="39"/>
-      <c r="F82" s="39">
+      <c r="E82" s="32"/>
+      <c r="F82" s="32">
         <v>313653</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="39">
+      <c r="A83" s="32">
         <v>1409</v>
       </c>
-      <c r="B83" s="39" t="s">
+      <c r="B83" s="32" t="s">
         <v>241</v>
       </c>
-      <c r="C83" s="39" t="s">
+      <c r="C83" s="32" t="s">
         <v>242</v>
       </c>
-      <c r="D83" s="39">
+      <c r="D83" s="32">
         <f t="shared" si="1"/>
         <v>1409</v>
       </c>
-      <c r="E83" s="39"/>
-      <c r="F83" s="39">
+      <c r="E83" s="32"/>
+      <c r="F83" s="32">
         <v>313654</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="39">
+      <c r="A84" s="32">
         <v>1410</v>
       </c>
-      <c r="B84" s="39" t="s">
+      <c r="B84" s="32" t="s">
         <v>243</v>
       </c>
-      <c r="C84" s="39" t="s">
+      <c r="C84" s="32" t="s">
         <v>244</v>
       </c>
-      <c r="D84" s="39">
+      <c r="D84" s="32">
         <f t="shared" si="1"/>
         <v>1410</v>
       </c>
-      <c r="E84" s="39"/>
-      <c r="F84" s="39">
+      <c r="E84" s="32"/>
+      <c r="F84" s="32">
         <v>313655</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="39">
+      <c r="A85" s="32">
         <v>1445</v>
       </c>
-      <c r="B85" s="39" t="s">
+      <c r="B85" s="32" t="s">
         <v>245</v>
       </c>
-      <c r="C85" s="39" t="s">
+      <c r="C85" s="32" t="s">
         <v>246</v>
       </c>
-      <c r="D85" s="39">
+      <c r="D85" s="32">
         <f t="shared" si="1"/>
         <v>1445</v>
       </c>
-      <c r="E85" s="39"/>
-      <c r="F85" s="39">
+      <c r="E85" s="32"/>
+      <c r="F85" s="32">
         <v>313680</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="39">
+      <c r="A86" s="32">
         <v>831</v>
       </c>
-      <c r="B86" s="39" t="s">
+      <c r="B86" s="32" t="s">
         <v>247</v>
       </c>
-      <c r="C86" s="39" t="s">
+      <c r="C86" s="32" t="s">
         <v>248</v>
       </c>
-      <c r="D86" s="39">
+      <c r="D86" s="32">
         <f t="shared" si="1"/>
         <v>831</v>
       </c>
-      <c r="E86" s="39"/>
-      <c r="F86" s="39">
+      <c r="E86" s="32"/>
+      <c r="F86" s="32">
         <v>313699</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="39">
+      <c r="A87" s="32">
         <v>840</v>
       </c>
-      <c r="B87" s="39" t="s">
+      <c r="B87" s="32" t="s">
         <v>249</v>
       </c>
-      <c r="C87" s="39" t="s">
+      <c r="C87" s="32" t="s">
         <v>250</v>
       </c>
-      <c r="D87" s="39">
+      <c r="D87" s="32">
         <f t="shared" si="1"/>
         <v>840</v>
       </c>
-      <c r="E87" s="39"/>
-      <c r="F87" s="39">
+      <c r="E87" s="32"/>
+      <c r="F87" s="32">
         <v>313709</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="39">
+      <c r="A88" s="32">
         <v>841</v>
       </c>
-      <c r="B88" s="39" t="s">
+      <c r="B88" s="32" t="s">
         <v>251</v>
       </c>
-      <c r="C88" s="39" t="s">
+      <c r="C88" s="32" t="s">
         <v>252</v>
       </c>
-      <c r="D88" s="39">
+      <c r="D88" s="32">
         <f t="shared" si="1"/>
         <v>841</v>
       </c>
-      <c r="E88" s="39"/>
-      <c r="F88" s="39">
+      <c r="E88" s="32"/>
+      <c r="F88" s="32">
         <v>313710</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="39">
+      <c r="A89" s="32">
         <v>1487</v>
       </c>
-      <c r="B89" s="39" t="s">
+      <c r="B89" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="C89" s="39" t="s">
+      <c r="C89" s="32" t="s">
         <v>254</v>
       </c>
-      <c r="D89" s="39">
+      <c r="D89" s="32">
         <f t="shared" si="1"/>
         <v>1487</v>
       </c>
-      <c r="E89" s="39"/>
-      <c r="F89" s="39">
+      <c r="E89" s="32"/>
+      <c r="F89" s="32">
         <v>313742</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="39">
+      <c r="A90" s="32">
         <v>1412</v>
       </c>
-      <c r="B90" s="39" t="s">
+      <c r="B90" s="32" t="s">
         <v>255</v>
       </c>
-      <c r="C90" s="39" t="s">
+      <c r="C90" s="32" t="s">
         <v>256</v>
       </c>
-      <c r="D90" s="39">
+      <c r="D90" s="32">
         <f t="shared" si="1"/>
         <v>1412</v>
       </c>
-      <c r="E90" s="39"/>
-      <c r="F90" s="39">
+      <c r="E90" s="32"/>
+      <c r="F90" s="32">
         <v>313756</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="39">
+      <c r="A91" s="32">
         <v>1414</v>
       </c>
-      <c r="B91" s="39" t="s">
+      <c r="B91" s="32" t="s">
         <v>257</v>
       </c>
-      <c r="C91" s="39" t="s">
+      <c r="C91" s="32" t="s">
         <v>258</v>
       </c>
-      <c r="D91" s="39">
+      <c r="D91" s="32">
         <f t="shared" si="1"/>
         <v>1414</v>
       </c>
-      <c r="E91" s="39"/>
-      <c r="F91" s="39">
+      <c r="E91" s="32"/>
+      <c r="F91" s="32">
         <v>313758</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="39">
+      <c r="A92" s="32">
         <v>1004</v>
       </c>
-      <c r="B92" s="39" t="s">
+      <c r="B92" s="32" t="s">
         <v>259</v>
       </c>
-      <c r="C92" s="39" t="s">
+      <c r="C92" s="32" t="s">
         <v>260</v>
       </c>
-      <c r="D92" s="39">
+      <c r="D92" s="32">
         <f t="shared" si="1"/>
         <v>1004</v>
       </c>
-      <c r="E92" s="39"/>
-      <c r="F92" s="39">
+      <c r="E92" s="32"/>
+      <c r="F92" s="32">
         <v>313759</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="39">
+      <c r="A93" s="32">
         <v>1007</v>
       </c>
-      <c r="B93" s="39" t="s">
+      <c r="B93" s="32" t="s">
         <v>261</v>
       </c>
-      <c r="C93" s="39" t="s">
+      <c r="C93" s="32" t="s">
         <v>262</v>
       </c>
-      <c r="D93" s="39">
+      <c r="D93" s="32">
         <f t="shared" si="1"/>
         <v>1007</v>
       </c>
-      <c r="E93" s="39"/>
-      <c r="F93" s="39">
+      <c r="E93" s="32"/>
+      <c r="F93" s="32">
         <v>313760</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="39">
+      <c r="A94" s="32">
         <v>1422</v>
       </c>
-      <c r="B94" s="39" t="s">
+      <c r="B94" s="32" t="s">
         <v>263</v>
       </c>
-      <c r="C94" s="39" t="s">
+      <c r="C94" s="32" t="s">
         <v>264</v>
       </c>
-      <c r="D94" s="39">
+      <c r="D94" s="32">
         <f t="shared" si="1"/>
         <v>1422</v>
       </c>
-      <c r="E94" s="39"/>
-      <c r="F94" s="39">
+      <c r="E94" s="32"/>
+      <c r="F94" s="32">
         <v>313761</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="39">
+      <c r="A95" s="32">
         <v>1010</v>
       </c>
-      <c r="B95" s="39" t="s">
+      <c r="B95" s="32" t="s">
         <v>265</v>
       </c>
-      <c r="C95" s="39" t="s">
+      <c r="C95" s="32" t="s">
         <v>266</v>
       </c>
-      <c r="D95" s="39">
+      <c r="D95" s="32">
         <f t="shared" si="1"/>
         <v>1010</v>
       </c>
-      <c r="E95" s="39"/>
-      <c r="F95" s="39">
+      <c r="E95" s="32"/>
+      <c r="F95" s="32">
         <v>313762</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="39">
+      <c r="A96" s="32">
         <v>1423</v>
       </c>
-      <c r="B96" s="39" t="s">
+      <c r="B96" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="C96" s="39" t="s">
+      <c r="C96" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="D96" s="39">
+      <c r="D96" s="32">
         <f t="shared" si="1"/>
         <v>1423</v>
       </c>
-      <c r="E96" s="39"/>
-      <c r="F96" s="39">
+      <c r="E96" s="32"/>
+      <c r="F96" s="32">
         <v>313763</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" s="39">
+      <c r="A97" s="32">
         <v>1552</v>
       </c>
-      <c r="B97" s="39" t="s">
+      <c r="B97" s="32" t="s">
         <v>267</v>
       </c>
-      <c r="C97" s="39" t="s">
+      <c r="C97" s="32" t="s">
         <v>268</v>
       </c>
-      <c r="D97" s="39">
+      <c r="D97" s="32">
         <f t="shared" si="1"/>
         <v>1552</v>
       </c>
-      <c r="E97" s="39"/>
-      <c r="F97" s="39">
+      <c r="E97" s="32"/>
+      <c r="F97" s="32">
         <v>313820</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" s="39">
+      <c r="A98" s="32">
         <v>1501</v>
       </c>
-      <c r="B98" s="39" t="s">
+      <c r="B98" s="32" t="s">
         <v>269</v>
       </c>
-      <c r="C98" s="39" t="s">
+      <c r="C98" s="32" t="s">
         <v>270</v>
       </c>
-      <c r="D98" s="39">
+      <c r="D98" s="32">
         <f t="shared" si="1"/>
         <v>1501</v>
       </c>
-      <c r="E98" s="39"/>
-      <c r="F98" s="39">
+      <c r="E98" s="32"/>
+      <c r="F98" s="32">
         <v>313764</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99" s="39">
+      <c r="A99" s="32">
         <v>1507</v>
       </c>
-      <c r="B99" s="39" t="s">
+      <c r="B99" s="32" t="s">
         <v>271</v>
       </c>
-      <c r="C99" s="39" t="s">
+      <c r="C99" s="32" t="s">
         <v>272</v>
       </c>
-      <c r="D99" s="39">
+      <c r="D99" s="32">
         <f t="shared" si="1"/>
         <v>1507</v>
       </c>
-      <c r="E99" s="39"/>
-      <c r="F99" s="39">
+      <c r="E99" s="32"/>
+      <c r="F99" s="32">
         <v>313770</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" s="39">
+      <c r="A100" s="32">
         <v>1508</v>
       </c>
-      <c r="B100" s="39" t="s">
+      <c r="B100" s="32" t="s">
         <v>273</v>
       </c>
-      <c r="C100" s="39" t="s">
+      <c r="C100" s="32" t="s">
         <v>274</v>
       </c>
-      <c r="D100" s="39">
+      <c r="D100" s="32">
         <f t="shared" si="1"/>
         <v>1508</v>
       </c>
-      <c r="E100" s="39"/>
-      <c r="F100" s="39">
+      <c r="E100" s="32"/>
+      <c r="F100" s="32">
         <v>313771</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101" s="39">
+      <c r="A101" s="32">
         <v>1511</v>
       </c>
-      <c r="B101" s="39" t="s">
+      <c r="B101" s="32" t="s">
         <v>275</v>
       </c>
-      <c r="C101" s="39" t="s">
+      <c r="C101" s="32" t="s">
         <v>276</v>
       </c>
-      <c r="D101" s="39">
+      <c r="D101" s="32">
         <f t="shared" si="1"/>
         <v>1511</v>
       </c>
-      <c r="E101" s="39"/>
-      <c r="F101" s="39">
+      <c r="E101" s="32"/>
+      <c r="F101" s="32">
         <v>313774</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102" s="39">
+      <c r="A102" s="32">
         <v>896</v>
       </c>
-      <c r="B102" s="39" t="s">
+      <c r="B102" s="32" t="s">
         <v>277</v>
       </c>
-      <c r="C102" s="39" t="s">
+      <c r="C102" s="32" t="s">
         <v>278</v>
       </c>
-      <c r="D102" s="39">
+      <c r="D102" s="32">
         <f t="shared" si="1"/>
         <v>896</v>
       </c>
-      <c r="E102" s="39"/>
-      <c r="F102" s="39">
+      <c r="E102" s="32"/>
+      <c r="F102" s="32">
         <v>313205</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" s="39">
+      <c r="A103" s="32">
         <v>931</v>
       </c>
-      <c r="B103" s="39" t="s">
+      <c r="B103" s="32" t="s">
         <v>279</v>
       </c>
-      <c r="C103" s="39" t="s">
+      <c r="C103" s="32" t="s">
         <v>280</v>
       </c>
-      <c r="D103" s="39">
+      <c r="D103" s="32">
         <f t="shared" si="1"/>
         <v>931</v>
       </c>
-      <c r="E103" s="39"/>
-      <c r="F103" s="39">
+      <c r="E103" s="32"/>
+      <c r="F103" s="32">
         <v>310139</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" s="39">
+      <c r="A104" s="32">
         <v>1034</v>
       </c>
-      <c r="B104" s="39" t="s">
+      <c r="B104" s="32" t="s">
         <v>281</v>
       </c>
-      <c r="C104" s="39" t="s">
+      <c r="C104" s="32" t="s">
         <v>282</v>
       </c>
-      <c r="D104" s="39">
+      <c r="D104" s="32">
         <f t="shared" si="1"/>
         <v>1034</v>
       </c>
-      <c r="E104" s="39"/>
-      <c r="F104" s="39">
+      <c r="E104" s="32"/>
+      <c r="F104" s="32">
         <v>313302</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="39">
+      <c r="A105" s="32">
         <v>1111</v>
       </c>
-      <c r="B105" s="39" t="s">
+      <c r="B105" s="32" t="s">
         <v>283</v>
       </c>
-      <c r="C105" s="39" t="s">
+      <c r="C105" s="32" t="s">
         <v>284</v>
       </c>
-      <c r="D105" s="39">
+      <c r="D105" s="32">
         <f t="shared" si="1"/>
         <v>1111</v>
       </c>
-      <c r="E105" s="39"/>
-      <c r="F105" s="39">
+      <c r="E105" s="32"/>
+      <c r="F105" s="32">
         <v>313362</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="39">
+      <c r="A106" s="32">
         <v>1046</v>
       </c>
-      <c r="B106" s="39" t="s">
+      <c r="B106" s="32" t="s">
         <v>285</v>
       </c>
-      <c r="C106" s="39" t="s">
+      <c r="C106" s="32" t="s">
         <v>286</v>
       </c>
-      <c r="D106" s="39">
+      <c r="D106" s="32">
         <f t="shared" si="1"/>
         <v>1046</v>
       </c>
-      <c r="E106" s="39"/>
-      <c r="F106" s="39">
+      <c r="E106" s="32"/>
+      <c r="F106" s="32">
         <v>313314</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" s="39">
+      <c r="A107" s="32">
         <v>1534</v>
       </c>
-      <c r="B107" s="39" t="s">
+      <c r="B107" s="32" t="s">
         <v>287</v>
       </c>
-      <c r="C107" s="39" t="s">
+      <c r="C107" s="32" t="s">
         <v>288</v>
       </c>
-      <c r="D107" s="39">
+      <c r="D107" s="32">
         <f t="shared" si="1"/>
         <v>1534</v>
       </c>
-      <c r="E107" s="39"/>
-      <c r="F107" s="39">
+      <c r="E107" s="32"/>
+      <c r="F107" s="32">
         <v>313802</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A108" s="39">
+      <c r="A108" s="32">
         <v>1543</v>
       </c>
-      <c r="B108" s="39" t="s">
+      <c r="B108" s="32" t="s">
         <v>289</v>
       </c>
-      <c r="C108" s="39" t="s">
+      <c r="C108" s="32" t="s">
         <v>290</v>
       </c>
-      <c r="D108" s="39">
+      <c r="D108" s="32">
         <f t="shared" si="1"/>
         <v>1543</v>
       </c>
-      <c r="E108" s="39"/>
-      <c r="F108" s="39">
+      <c r="E108" s="32"/>
+      <c r="F108" s="32">
         <v>313811</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A109" s="39">
+      <c r="A109" s="32">
         <v>1570</v>
       </c>
-      <c r="B109" s="39" t="s">
+      <c r="B109" s="32" t="s">
         <v>291</v>
       </c>
-      <c r="C109" s="39" t="s">
+      <c r="C109" s="32" t="s">
         <v>292</v>
       </c>
-      <c r="D109" s="39">
+      <c r="D109" s="32">
         <f t="shared" si="1"/>
         <v>1570</v>
       </c>
-      <c r="E109" s="39"/>
-      <c r="F109" s="39">
+      <c r="E109" s="32"/>
+      <c r="F109" s="32">
         <v>313838</v>
       </c>
     </row>
@@ -5763,270 +5836,270 @@
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" style="40" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="45" style="40" customWidth="1"/>
-    <col min="3" max="3" width="44.5703125" style="40" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="33.5703125" style="40" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="37.7109375" style="40" hidden="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="40"/>
+    <col min="1" max="1" width="18.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45" style="33" customWidth="1"/>
+    <col min="3" max="3" width="44.5703125" style="33" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="33.5703125" style="33" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="37.7109375" style="33" hidden="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="33"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="41" t="s">
         <v>555</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="42" t="s">
         <v>556</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="C1" s="38" t="s">
         <v>324</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="36" t="s">
         <v>485</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="E1" s="35" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="39">
-        <v>1</v>
-      </c>
-      <c r="B2" s="39" t="s">
+      <c r="A2" s="32">
+        <v>1</v>
+      </c>
+      <c r="B2" s="32" t="s">
         <v>294</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="32" t="s">
         <v>295</v>
       </c>
-      <c r="D2" s="44">
+      <c r="D2" s="37">
         <f>A2</f>
         <v>1</v>
       </c>
-      <c r="E2" s="44"/>
+      <c r="E2" s="37"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="39">
+      <c r="A3" s="32">
         <v>2</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="32" t="s">
         <v>296</v>
       </c>
-      <c r="C3" s="39" t="s">
+      <c r="C3" s="32" t="s">
         <v>297</v>
       </c>
-      <c r="D3" s="39">
+      <c r="D3" s="32">
         <f t="shared" ref="D3:D16" si="0">A3</f>
         <v>2</v>
       </c>
-      <c r="E3" s="39"/>
+      <c r="E3" s="32"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="39">
+      <c r="A4" s="32">
         <v>3</v>
       </c>
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="32" t="s">
         <v>298</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="32" t="s">
         <v>299</v>
       </c>
-      <c r="D4" s="39">
+      <c r="D4" s="32">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="E4" s="39"/>
+      <c r="E4" s="32"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="39">
+      <c r="A5" s="32">
         <v>4</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="32" t="s">
         <v>300</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="C5" s="32" t="s">
         <v>301</v>
       </c>
-      <c r="D5" s="39">
+      <c r="D5" s="32">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E5" s="39"/>
+      <c r="E5" s="32"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="39">
+      <c r="A6" s="32">
         <v>5</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="32" t="s">
         <v>302</v>
       </c>
-      <c r="C6" s="39" t="s">
+      <c r="C6" s="32" t="s">
         <v>303</v>
       </c>
-      <c r="D6" s="39">
+      <c r="D6" s="32">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="E6" s="39"/>
+      <c r="E6" s="32"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="39">
+      <c r="A7" s="32">
         <v>7</v>
       </c>
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="32" t="s">
         <v>304</v>
       </c>
-      <c r="C7" s="39" t="s">
+      <c r="C7" s="32" t="s">
         <v>305</v>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="32">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="E7" s="39"/>
+      <c r="E7" s="32"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="39">
+      <c r="A8" s="32">
         <v>8</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="C8" s="39" t="s">
+      <c r="C8" s="32" t="s">
         <v>307</v>
       </c>
-      <c r="D8" s="39">
+      <c r="D8" s="32">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="E8" s="39"/>
+      <c r="E8" s="32"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="39">
+      <c r="A9" s="32">
         <v>9</v>
       </c>
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="32" t="s">
         <v>308</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="32" t="s">
         <v>309</v>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="32">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="E9" s="39"/>
+      <c r="E9" s="32"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="39">
+      <c r="A10" s="32">
         <v>10</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="32" t="s">
         <v>310</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="32" t="s">
         <v>311</v>
       </c>
-      <c r="D10" s="39">
+      <c r="D10" s="32">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="E10" s="39"/>
+      <c r="E10" s="32"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="39">
+      <c r="A11" s="32">
         <v>11</v>
       </c>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="32" t="s">
         <v>312</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="32" t="s">
         <v>313</v>
       </c>
-      <c r="D11" s="39">
+      <c r="D11" s="32">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="E11" s="39"/>
+      <c r="E11" s="32"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="39">
+      <c r="A12" s="32">
         <v>12</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="32" t="s">
         <v>314</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="32" t="s">
         <v>315</v>
       </c>
-      <c r="D12" s="39">
+      <c r="D12" s="32">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="E12" s="39"/>
+      <c r="E12" s="32"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="39">
+      <c r="A13" s="32">
         <v>13</v>
       </c>
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="32" t="s">
         <v>316</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="32" t="s">
         <v>317</v>
       </c>
-      <c r="D13" s="39">
+      <c r="D13" s="32">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="E13" s="39"/>
+      <c r="E13" s="32"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="39">
+      <c r="A14" s="32">
         <v>14</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="32" t="s">
         <v>318</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="32" t="s">
         <v>319</v>
       </c>
-      <c r="D14" s="39">
+      <c r="D14" s="32">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="E14" s="39"/>
+      <c r="E14" s="32"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="39">
+      <c r="A15" s="32">
         <v>15</v>
       </c>
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="32" t="s">
         <v>320</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C15" s="32" t="s">
         <v>321</v>
       </c>
-      <c r="D15" s="39">
+      <c r="D15" s="32">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="E15" s="39"/>
+      <c r="E15" s="32"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="39">
+      <c r="A16" s="32">
         <v>16</v>
       </c>
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="32" t="s">
         <v>322</v>
       </c>
-      <c r="C16" s="39" t="s">
+      <c r="C16" s="32" t="s">
         <v>323</v>
       </c>
-      <c r="D16" s="39">
+      <c r="D16" s="32">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="E16" s="39"/>
+      <c r="E16" s="32"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6038,354 +6111,354 @@
   <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16" style="40" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.5703125" style="40" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.5703125" style="40" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="32.5703125" style="40" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="28.5703125" style="40" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" style="40" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="40"/>
-    <col min="8" max="8" width="13.5703125" style="40" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="32.140625" style="40" customWidth="1"/>
-    <col min="10" max="10" width="35.85546875" style="40" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="40"/>
+    <col min="1" max="1" width="16" style="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.5703125" style="33" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="32.5703125" style="33" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="28.5703125" style="33" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" style="33" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="33"/>
+    <col min="8" max="8" width="13.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32.140625" style="33" customWidth="1"/>
+    <col min="10" max="10" width="35.85546875" style="33" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="33"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="34" t="s">
         <v>557</v>
       </c>
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="35" t="s">
         <v>558</v>
       </c>
-      <c r="C1" s="42" t="s">
+      <c r="C1" s="35" t="s">
         <v>349</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="36" t="s">
         <v>485</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="E1" s="35" t="s">
         <v>486</v>
       </c>
-      <c r="G1" s="53"/>
+      <c r="G1" s="46"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="50">
+      <c r="A2" s="43">
         <v>4</v>
       </c>
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="43" t="s">
         <v>325</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="C2" s="43" t="s">
         <v>326</v>
       </c>
-      <c r="D2" s="44">
+      <c r="D2" s="37">
         <f>A2</f>
         <v>4</v>
       </c>
-      <c r="E2" s="44"/>
+      <c r="E2" s="37"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="51">
+      <c r="A3" s="44">
         <v>5</v>
       </c>
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="44" t="s">
         <v>327</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="44" t="s">
         <v>328</v>
       </c>
-      <c r="D3" s="39">
+      <c r="D3" s="32">
         <f t="shared" ref="D3:D13" si="0">A3</f>
         <v>5</v>
       </c>
-      <c r="E3" s="39"/>
+      <c r="E3" s="32"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="51">
+      <c r="A4" s="44">
         <v>6</v>
       </c>
-      <c r="B4" s="51" t="s">
+      <c r="B4" s="44" t="s">
         <v>329</v>
       </c>
-      <c r="C4" s="51" t="s">
+      <c r="C4" s="44" t="s">
         <v>330</v>
       </c>
-      <c r="D4" s="39">
+      <c r="D4" s="32">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="E4" s="39"/>
+      <c r="E4" s="32"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="51">
+      <c r="A5" s="44">
         <v>7</v>
       </c>
-      <c r="B5" s="51" t="s">
+      <c r="B5" s="44" t="s">
         <v>331</v>
       </c>
-      <c r="C5" s="51" t="s">
+      <c r="C5" s="44" t="s">
         <v>332</v>
       </c>
-      <c r="D5" s="39">
+      <c r="D5" s="32">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="E5" s="39"/>
+      <c r="E5" s="32"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="51">
+      <c r="A6" s="44">
         <v>8</v>
       </c>
-      <c r="B6" s="51" t="s">
+      <c r="B6" s="44" t="s">
         <v>333</v>
       </c>
-      <c r="C6" s="51" t="s">
+      <c r="C6" s="44" t="s">
         <v>334</v>
       </c>
-      <c r="D6" s="39">
+      <c r="D6" s="32">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="E6" s="39"/>
+      <c r="E6" s="32"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="51">
+      <c r="A7" s="44">
         <v>9</v>
       </c>
-      <c r="B7" s="51" t="s">
+      <c r="B7" s="44" t="s">
         <v>335</v>
       </c>
-      <c r="C7" s="51" t="s">
+      <c r="C7" s="44" t="s">
         <v>336</v>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="32">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="E7" s="39"/>
+      <c r="E7" s="32"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="51">
+      <c r="A8" s="44">
         <v>10</v>
       </c>
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="44" t="s">
         <v>337</v>
       </c>
-      <c r="C8" s="51" t="s">
+      <c r="C8" s="44" t="s">
         <v>338</v>
       </c>
-      <c r="D8" s="39">
+      <c r="D8" s="32">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="E8" s="39"/>
+      <c r="E8" s="32"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="51">
+      <c r="A9" s="44">
         <v>11</v>
       </c>
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="44" t="s">
         <v>339</v>
       </c>
-      <c r="C9" s="51" t="s">
+      <c r="C9" s="44" t="s">
         <v>340</v>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="32">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="E9" s="39"/>
+      <c r="E9" s="32"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="51">
+      <c r="A10" s="44">
         <v>12</v>
       </c>
-      <c r="B10" s="51" t="s">
+      <c r="B10" s="44" t="s">
         <v>341</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="C10" s="44" t="s">
         <v>342</v>
       </c>
-      <c r="D10" s="39">
+      <c r="D10" s="32">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="E10" s="39"/>
+      <c r="E10" s="32"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="51">
-        <v>1</v>
-      </c>
-      <c r="B11" s="51" t="s">
+      <c r="A11" s="44">
+        <v>1</v>
+      </c>
+      <c r="B11" s="44" t="s">
         <v>343</v>
       </c>
-      <c r="C11" s="51" t="s">
+      <c r="C11" s="44" t="s">
         <v>344</v>
       </c>
-      <c r="D11" s="39">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E11" s="39"/>
+      <c r="D11" s="32">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E11" s="32"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="51">
+      <c r="A12" s="44">
         <v>2</v>
       </c>
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="44" t="s">
         <v>345</v>
       </c>
-      <c r="C12" s="51" t="s">
+      <c r="C12" s="44" t="s">
         <v>346</v>
       </c>
-      <c r="D12" s="39">
+      <c r="D12" s="32">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="E12" s="39"/>
+      <c r="E12" s="32"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="51">
+      <c r="A13" s="44">
         <v>3</v>
       </c>
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="44" t="s">
         <v>347</v>
       </c>
-      <c r="C13" s="51" t="s">
+      <c r="C13" s="44" t="s">
         <v>348</v>
       </c>
-      <c r="D13" s="39">
+      <c r="D13" s="32">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="E13" s="39"/>
+      <c r="E13" s="32"/>
     </row>
     <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="37" t="s">
+      <c r="A18" s="30" t="s">
         <v>350</v>
       </c>
-      <c r="B18" s="52" t="s">
+      <c r="B18" s="45" t="s">
         <v>485</v>
       </c>
-      <c r="C18" s="54" t="s">
+      <c r="C18" s="47" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="39" t="s">
+      <c r="A19" s="32" t="s">
         <v>351</v>
       </c>
-      <c r="B19" s="39" t="str">
+      <c r="B19" s="32" t="str">
         <f>A19</f>
         <v>Q1 Apr to Jun</v>
       </c>
-      <c r="C19" s="39"/>
+      <c r="C19" s="32"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="39" t="s">
+      <c r="A20" s="32" t="s">
         <v>352</v>
       </c>
-      <c r="B20" s="39" t="str">
+      <c r="B20" s="32" t="str">
         <f>A20</f>
         <v>Q2 Jul to Sep</v>
       </c>
-      <c r="C20" s="39"/>
+      <c r="C20" s="32"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="39" t="s">
+      <c r="A21" s="32" t="s">
         <v>353</v>
       </c>
-      <c r="B21" s="39" t="str">
+      <c r="B21" s="32" t="str">
         <f>A21</f>
         <v>Q3 Oct to Dec</v>
       </c>
-      <c r="C21" s="39"/>
+      <c r="C21" s="32"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="39" t="s">
+      <c r="A22" s="32" t="s">
         <v>354</v>
       </c>
-      <c r="B22" s="39" t="str">
+      <c r="B22" s="32" t="str">
         <f>A22</f>
         <v>Q4 Jan to Mar</v>
       </c>
-      <c r="C22" s="39"/>
+      <c r="C22" s="32"/>
     </row>
     <row r="24" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="54" t="s">
+      <c r="A25" s="47" t="s">
         <v>355</v>
       </c>
-      <c r="B25" s="52" t="s">
+      <c r="B25" s="45" t="s">
         <v>485</v>
       </c>
-      <c r="C25" s="54" t="s">
+      <c r="C25" s="47" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="39" t="s">
+      <c r="A26" s="32" t="s">
         <v>356</v>
       </c>
-      <c r="B26" s="39" t="str">
+      <c r="B26" s="32" t="str">
         <f>A26</f>
         <v>B1 Apr To Sep</v>
       </c>
-      <c r="C26" s="39"/>
+      <c r="C26" s="32"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="39" t="s">
+      <c r="A27" s="32" t="s">
         <v>357</v>
       </c>
-      <c r="B27" s="39" t="str">
+      <c r="B27" s="32" t="str">
         <f>A27</f>
         <v>B2 Oct To Mar</v>
       </c>
-      <c r="C27" s="39"/>
+      <c r="C27" s="32"/>
     </row>
     <row r="29" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="54" t="s">
+      <c r="A30" s="47" t="s">
         <v>358</v>
       </c>
-      <c r="B30" s="52" t="s">
+      <c r="B30" s="45" t="s">
         <v>485</v>
       </c>
-      <c r="C30" s="54" t="s">
+      <c r="C30" s="47" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="39" t="s">
+      <c r="A31" s="32" t="s">
         <v>359</v>
       </c>
-      <c r="B31" s="39" t="str">
+      <c r="B31" s="32" t="str">
         <f>A31</f>
         <v>F1 Apr To Jul</v>
       </c>
-      <c r="C31" s="39"/>
+      <c r="C31" s="32"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="39" t="s">
+      <c r="A32" s="32" t="s">
         <v>360</v>
       </c>
-      <c r="B32" s="39" t="str">
+      <c r="B32" s="32" t="str">
         <f>A32</f>
         <v>F2 Aug To Nov</v>
       </c>
-      <c r="C32" s="39"/>
+      <c r="C32" s="32"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="39" t="s">
+      <c r="A33" s="32" t="s">
         <v>361</v>
       </c>
-      <c r="B33" s="39" t="str">
+      <c r="B33" s="32" t="str">
         <f>A33</f>
         <v>F3 Dec To Mar</v>
       </c>
-      <c r="C33" s="39"/>
+      <c r="C33" s="32"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6397,96 +6470,96 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" style="40" customWidth="1"/>
-    <col min="2" max="2" width="20.140625" style="40" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" style="40" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="32.85546875" style="40" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="33.85546875" style="40" hidden="1" customWidth="1"/>
-    <col min="6" max="8" width="0" style="40" hidden="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="40"/>
+    <col min="1" max="1" width="16.42578125" style="33" customWidth="1"/>
+    <col min="2" max="2" width="20.140625" style="33" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" style="33" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="32.85546875" style="33" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="33.85546875" style="33" hidden="1" customWidth="1"/>
+    <col min="6" max="8" width="0" style="33" hidden="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="33"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="40" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="39" t="s">
         <v>560</v>
       </c>
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="40" t="s">
         <v>559</v>
       </c>
-      <c r="C1" s="55" t="s">
+      <c r="C1" s="48" t="s">
         <v>372</v>
       </c>
-      <c r="D1" s="52" t="s">
+      <c r="D1" s="45" t="s">
         <v>485</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="E1" s="47" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="40" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="39">
-        <v>1</v>
-      </c>
-      <c r="B2" s="39" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="32">
+        <v>1</v>
+      </c>
+      <c r="B2" s="32" t="s">
         <v>362</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="32" t="s">
         <v>363</v>
       </c>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-    </row>
-    <row r="3" spans="1:5" s="40" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="39">
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="32">
         <v>2</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="32" t="s">
         <v>364</v>
       </c>
-      <c r="C3" s="39" t="s">
+      <c r="C3" s="32" t="s">
         <v>365</v>
       </c>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-    </row>
-    <row r="4" spans="1:5" s="40" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="39">
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="32">
         <v>3</v>
       </c>
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="32" t="s">
         <v>366</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="32" t="s">
         <v>367</v>
       </c>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-    </row>
-    <row r="5" spans="1:5" s="40" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="39">
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="32">
         <v>4</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="32" t="s">
         <v>368</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="C5" s="32" t="s">
         <v>369</v>
       </c>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-    </row>
-    <row r="6" spans="1:5" s="40" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="39">
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="32">
         <v>5</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="32" t="s">
         <v>358</v>
       </c>
-      <c r="C6" s="39" t="s">
+      <c r="C6" s="32" t="s">
         <v>370</v>
       </c>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6495,7 +6568,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -6507,7 +6580,9 @@
     <col min="7" max="7" width="18.42578125" style="3" customWidth="1"/>
     <col min="8" max="8" width="43.140625" style="3" customWidth="1"/>
     <col min="9" max="9" width="45.28515625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="1"/>
+    <col min="10" max="12" width="9.140625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="30.7109375" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6539,7 +6614,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>430</v>
       </c>
@@ -6567,7 +6642,7 @@
       </c>
       <c r="I2" s="14"/>
     </row>
-    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>431</v>
       </c>
@@ -6595,7 +6670,7 @@
       </c>
       <c r="I3" s="6"/>
     </row>
-    <row r="4" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>432</v>
       </c>
@@ -6623,7 +6698,7 @@
       </c>
       <c r="I4" s="6"/>
     </row>
-    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>433</v>
       </c>
@@ -6651,7 +6726,7 @@
       </c>
       <c r="I5" s="6"/>
     </row>
-    <row r="6" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>434</v>
       </c>
@@ -6679,7 +6754,7 @@
       </c>
       <c r="I6" s="6"/>
     </row>
-    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>435</v>
       </c>
@@ -6707,7 +6782,7 @@
       </c>
       <c r="I7" s="6"/>
     </row>
-    <row r="8" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>436</v>
       </c>
@@ -6735,7 +6810,7 @@
       </c>
       <c r="I8" s="6"/>
     </row>
-    <row r="9" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>437</v>
       </c>
@@ -6763,7 +6838,7 @@
       </c>
       <c r="I9" s="6"/>
     </row>
-    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>438</v>
       </c>
@@ -6791,7 +6866,7 @@
       </c>
       <c r="I10" s="6"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>439</v>
       </c>
@@ -6819,7 +6894,7 @@
       </c>
       <c r="I11" s="6"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>440</v>
       </c>
@@ -6847,7 +6922,7 @@
       </c>
       <c r="I12" s="6"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>441</v>
       </c>
@@ -6875,7 +6950,7 @@
       </c>
       <c r="I13" s="6"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>442</v>
       </c>
@@ -6903,7 +6978,7 @@
       </c>
       <c r="I14" s="6"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>443</v>
       </c>
@@ -6931,7 +7006,7 @@
       </c>
       <c r="I15" s="6"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>444</v>
       </c>
@@ -6959,7 +7034,7 @@
       </c>
       <c r="I16" s="6"/>
     </row>
-    <row r="17" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>445</v>
       </c>
@@ -6987,7 +7062,7 @@
       </c>
       <c r="I17" s="6"/>
     </row>
-    <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>446</v>
       </c>
@@ -7015,26 +7090,26 @@
       </c>
       <c r="I18" s="6"/>
     </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="30" t="s">
+    <row r="19" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="51" t="s">
         <v>447</v>
       </c>
-      <c r="B19" s="31" t="s">
+      <c r="B19" s="52" t="s">
         <v>391</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" s="53" t="s">
         <v>480</v>
       </c>
-      <c r="D19" s="33">
-        <v>1</v>
-      </c>
-      <c r="E19" s="33">
+      <c r="D19" s="50">
+        <v>1</v>
+      </c>
+      <c r="E19" s="50">
         <v>2</v>
       </c>
-      <c r="F19" s="33">
-        <v>1</v>
-      </c>
-      <c r="G19" s="32">
+      <c r="F19" s="50">
+        <v>1</v>
+      </c>
+      <c r="G19" s="49">
         <v>2</v>
       </c>
       <c r="H19" s="15" t="str">
@@ -7043,35 +7118,35 @@
       </c>
       <c r="I19" s="6"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="30"/>
-      <c r="B20" s="31"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="32"/>
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="51"/>
+      <c r="B20" s="52"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="49"/>
       <c r="H20" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I20" s="6"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="30"/>
-      <c r="B21" s="31"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="32"/>
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="51"/>
+      <c r="B21" s="52"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="49"/>
       <c r="H21" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I21" s="6"/>
     </row>
-    <row r="22" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>448</v>
       </c>
@@ -7099,7 +7174,7 @@
       </c>
       <c r="I22" s="6"/>
     </row>
-    <row r="23" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>449</v>
       </c>
@@ -7127,7 +7202,7 @@
       </c>
       <c r="I23" s="6"/>
     </row>
-    <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>450</v>
       </c>
@@ -7155,7 +7230,7 @@
       </c>
       <c r="I24" s="6"/>
     </row>
-    <row r="25" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>451</v>
       </c>
@@ -7183,7 +7258,7 @@
       </c>
       <c r="I25" s="6"/>
     </row>
-    <row r="26" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>452</v>
       </c>
@@ -7211,7 +7286,7 @@
       </c>
       <c r="I26" s="6"/>
     </row>
-    <row r="27" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>453</v>
       </c>
@@ -7239,7 +7314,7 @@
       </c>
       <c r="I27" s="6"/>
     </row>
-    <row r="28" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>454</v>
       </c>
@@ -7267,7 +7342,7 @@
       </c>
       <c r="I28" s="6"/>
     </row>
-    <row r="29" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>455</v>
       </c>
@@ -7295,7 +7370,7 @@
       </c>
       <c r="I29" s="6"/>
     </row>
-    <row r="30" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>456</v>
       </c>
@@ -7323,7 +7398,7 @@
       </c>
       <c r="I30" s="6"/>
     </row>
-    <row r="31" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>457</v>
       </c>
@@ -7351,7 +7426,7 @@
       </c>
       <c r="I31" s="6"/>
     </row>
-    <row r="32" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>458</v>
       </c>
@@ -7379,7 +7454,7 @@
       </c>
       <c r="I32" s="6"/>
     </row>
-    <row r="33" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>459</v>
       </c>
@@ -7407,7 +7482,7 @@
       </c>
       <c r="I33" s="6"/>
     </row>
-    <row r="34" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>460</v>
       </c>
@@ -7435,7 +7510,7 @@
       </c>
       <c r="I34" s="6"/>
     </row>
-    <row r="35" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>461</v>
       </c>
@@ -7463,7 +7538,7 @@
       </c>
       <c r="I35" s="6"/>
     </row>
-    <row r="36" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>462</v>
       </c>
@@ -7491,7 +7566,7 @@
       </c>
       <c r="I36" s="6"/>
     </row>
-    <row r="37" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>463</v>
       </c>
@@ -7519,7 +7594,7 @@
       </c>
       <c r="I37" s="6"/>
     </row>
-    <row r="38" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>464</v>
       </c>
@@ -7547,7 +7622,7 @@
       </c>
       <c r="I38" s="6"/>
     </row>
-    <row r="39" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>465</v>
       </c>
@@ -7575,7 +7650,7 @@
       </c>
       <c r="I39" s="6"/>
     </row>
-    <row r="40" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>466</v>
       </c>
@@ -7603,7 +7678,7 @@
       </c>
       <c r="I40" s="6"/>
     </row>
-    <row r="41" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>467</v>
       </c>
@@ -7631,7 +7706,7 @@
       </c>
       <c r="I41" s="6"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>468</v>
       </c>
@@ -7659,26 +7734,26 @@
       </c>
       <c r="I42" s="6"/>
     </row>
-    <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="30" t="s">
+    <row r="43" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="51" t="s">
         <v>469</v>
       </c>
-      <c r="B43" s="31" t="s">
+      <c r="B43" s="52" t="s">
         <v>413</v>
       </c>
-      <c r="C43" s="34" t="s">
+      <c r="C43" s="53" t="s">
         <v>483</v>
       </c>
-      <c r="D43" s="33">
+      <c r="D43" s="50">
         <v>4</v>
       </c>
-      <c r="E43" s="33">
+      <c r="E43" s="50">
         <v>13</v>
       </c>
-      <c r="F43" s="33">
+      <c r="F43" s="50">
         <v>2</v>
       </c>
-      <c r="G43" s="32" t="s">
+      <c r="G43" s="49" t="s">
         <v>2</v>
       </c>
       <c r="H43" s="15" t="str">
@@ -7687,21 +7762,21 @@
       </c>
       <c r="I43" s="6"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="30"/>
-      <c r="B44" s="31"/>
-      <c r="C44" s="34"/>
-      <c r="D44" s="33"/>
-      <c r="E44" s="33"/>
-      <c r="F44" s="33"/>
-      <c r="G44" s="32"/>
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="51"/>
+      <c r="B44" s="52"/>
+      <c r="C44" s="53"/>
+      <c r="D44" s="50"/>
+      <c r="E44" s="50"/>
+      <c r="F44" s="50"/>
+      <c r="G44" s="49"/>
       <c r="H44" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I44" s="6"/>
     </row>
-    <row r="45" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>470</v>
       </c>
@@ -7729,7 +7804,7 @@
       </c>
       <c r="I45" s="6"/>
     </row>
-    <row r="46" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>471</v>
       </c>
@@ -7757,7 +7832,7 @@
       </c>
       <c r="I46" s="6"/>
     </row>
-    <row r="47" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>472</v>
       </c>
@@ -7785,7 +7860,7 @@
       </c>
       <c r="I47" s="6"/>
     </row>
-    <row r="48" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>473</v>
       </c>
@@ -7813,7 +7888,7 @@
       </c>
       <c r="I48" s="6"/>
     </row>
-    <row r="49" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>474</v>
       </c>
@@ -7841,7 +7916,7 @@
       </c>
       <c r="I49" s="6"/>
     </row>
-    <row r="50" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>475</v>
       </c>
@@ -7869,7 +7944,7 @@
       </c>
       <c r="I50" s="6"/>
     </row>
-    <row r="51" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>476</v>
       </c>
@@ -7953,7 +8028,7 @@
       </c>
       <c r="I53" s="6"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>479</v>
       </c>
@@ -7993,6 +8068,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="G19:G21"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="F19:F21"/>
+    <mergeCell ref="C19:C21"/>
     <mergeCell ref="G43:G44"/>
     <mergeCell ref="F43:F44"/>
     <mergeCell ref="D43:D44"/>
@@ -8000,13 +8082,6 @@
     <mergeCell ref="A43:A44"/>
     <mergeCell ref="B43:B44"/>
     <mergeCell ref="C43:C44"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="G19:G21"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="F19:F21"/>
-    <mergeCell ref="C19:C21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
